--- a/data-source/CeliacSafe_Datenbank_v4_Spain_129_geocoded.xlsx
+++ b/data-source/CeliacSafe_Datenbank_v4_Spain_129_geocoded.xlsx
@@ -607,9 +607,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -624,9 +622,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -676,9 +672,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -714,7 +708,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
@@ -792,7 +785,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -21394,7 +21386,11 @@
       </c>
       <c r="AM28" s="29" t="n"/>
       <c r="AN28" s="29" t="n"/>
-      <c r="AO28" s="29" t="n"/>
+      <c r="AO28" s="29" t="inlineStr">
+        <is>
+          <t>https://www.ubereats.com/es/store/solo-de-croquetas-reina-victoria/gJxlrNy-SbaD-TLK9Rd7xQ</t>
+        </is>
+      </c>
       <c r="AP28" s="29" t="inlineStr">
         <is>
           <t>https://www.ubereats.com/es/store/solo-de-croquetas-reina-victoria/gJxlrNy-SbaD-TLK9Rd7xQ</t>
@@ -28908,7 +28904,11 @@
           <t>https://mononokecafe.com/</t>
         </is>
       </c>
-      <c r="AU56" s="29" t="n"/>
+      <c r="AU56" s="29" t="inlineStr">
+        <is>
+          <t>https://mononokecafe.com/</t>
+        </is>
+      </c>
       <c r="AV56" s="29" t="inlineStr">
         <is>
           <t>not_checked</t>
@@ -31933,7 +31933,11 @@
         <v>0</v>
       </c>
       <c r="AM68" s="29" t="n"/>
-      <c r="AN68" s="29" t="n"/>
+      <c r="AN68" s="29" t="inlineStr">
+        <is>
+          <t>https://glovoapp.com/en/es/bilbao/stores/kuki-cookie-bakery-100-gluten-free-bilbao</t>
+        </is>
+      </c>
       <c r="AO68" s="29" t="n"/>
       <c r="AP68" s="29" t="n"/>
       <c r="AQ68" s="29" t="inlineStr">
@@ -40555,7 +40559,7 @@
       </c>
       <c r="BC103" s="29" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="BD103" s="90" t="n">
@@ -47002,7 +47006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC25"/>
+  <dimension ref="A1:BC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.53000068664551" customWidth="1" style="49" min="1" max="1"/>
@@ -47254,12 +47258,12 @@
       </c>
       <c r="I4" s="29" t="inlineStr">
         <is>
-          <t>verified_official_order_link</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J4" s="29" t="inlineStr">
         <is>
-          <t>https://restaurantewaraku.com/</t>
+          <t>Official website exposes Pide online / Delivery page.</t>
         </is>
       </c>
       <c r="K4" s="29" t="inlineStr">
@@ -47309,12 +47313,12 @@
       </c>
       <c r="I5" s="29" t="inlineStr">
         <is>
-          <t>verified_platform_profile</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J5" s="29" t="inlineStr">
         <is>
-          <t>https://www.ubereats.com/es/store/solo-de-croquetas-reina-victoria/gJxlrNy-SbaD-TLK9Rd7xQ</t>
+          <t>Direct Uber Eats listing found for the Reina Victoria location.</t>
         </is>
       </c>
       <c r="K5" s="29" t="inlineStr">
@@ -47364,12 +47368,12 @@
       </c>
       <c r="I6" s="29" t="inlineStr">
         <is>
-          <t>verified_platform_profile</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J6" s="29" t="inlineStr">
         <is>
-          <t>https://www.ubereats.com/es-en/store/grosso-napoletano-senza-glutine-cruz/SHY-9TMwXjS9evwYcVHK5Q</t>
+          <t>Direct Uber Eats listing found for the Cruz/Sol Senza Glutine location.</t>
         </is>
       </c>
       <c r="K6" s="29" t="inlineStr">
@@ -47419,12 +47423,12 @@
       </c>
       <c r="I7" s="29" t="inlineStr">
         <is>
-          <t>verified_platform_profile</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J7" s="29" t="inlineStr">
         <is>
-          <t>https://www.ubereats.com/es-en/store/ardemos-burgers-100-sin-gluten/3EiuS5McS0GtDLjJykKMPg</t>
+          <t>Direct Uber Eats listing found; listing names the venue as 100% sin gluten.</t>
         </is>
       </c>
       <c r="K7" s="29" t="inlineStr">
@@ -47474,12 +47478,12 @@
       </c>
       <c r="I8" s="29" t="inlineStr">
         <is>
-          <t>verified_platform_profile</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J8" s="29" t="inlineStr">
         <is>
-          <t>https://www.just-eat.es/restaurants-naked-and-sated-serrano-madrid/menu</t>
+          <t>Direct Just Eat listing found for Serrano branch.</t>
         </is>
       </c>
       <c r="K8" s="29" t="inlineStr">
@@ -47529,12 +47533,12 @@
       </c>
       <c r="I9" s="29" t="inlineStr">
         <is>
-          <t>verified_platform_profile</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J9" s="29" t="inlineStr">
         <is>
-          <t>https://www.just-eat.es/restaurants-pastramicalmariusbarcelona/menu</t>
+          <t>Direct Just Eat listing found for Cal Màrius 449.</t>
         </is>
       </c>
       <c r="K9" s="29" t="inlineStr">
@@ -48024,12 +48028,12 @@
       </c>
       <c r="I18" s="29" t="inlineStr">
         <is>
-          <t>verified_platform_profile</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J18" s="29" t="inlineStr">
         <is>
-          <t>https://glovoapp.com/en/es/bilbao/stores/kuki-cookie-bakery-100-gluten-free-bilbao</t>
+          <t>Direct Glovo listing found for Kuki Cookie Bakery 100% Gluten Free in Bilbao.</t>
         </is>
       </c>
       <c r="K18" s="29" t="inlineStr">
@@ -48378,6 +48382,556 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>Official Uber Eats listing found earlier; keep manual recheck before publishing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DL-ES-IB-MALLORCA-012-UBER_EATS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ES-IB-MALLORCA-012</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Can Pinyol Bakery</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Uber Eats</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.ubereats.com/es-en/store/can-pinyol-bakery/iSKw0rKUUM2-GGfvFxX27w</t>
+        </is>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>verified_from_commercial_links_audit</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Corrected from shifted source row; Uber Eats page is directly indexed and opens.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Corrected from shifted source row; Uber Eats page is directly indexed and opens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DL-ES-CT-BARCELONA-004-OWN_DELIVERY</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ES-CT-BARCELONA-004</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Aruku Provença</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Own delivery</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://arukubcn.com/provencia/</t>
+        </is>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>verified_from_commercial_links_audit</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Official location page offers takeaway/order path; platform URL still not published.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Official location page offers takeaway/order path; platform URL still not published.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DL-ES-CT-BARCELONA-005-OWN_DELIVERY</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ES-CT-BARCELONA-005</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Aruku Bruniquer</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Own delivery</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://arukubcn.com/</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>verified_from_commercial_links_audit</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Official site offers takeaway/order path; branch-specific platform URL still not published.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Official site offers takeaway/order path; branch-specific platform URL still not published.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DL-ES-VC-VALENCIA-004-OWN_DELIVERY</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ES-VC-VALENCIA-004</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>El Obrador del Celiaco</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Own delivery</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://elobradordelceliaco.com/</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>verified_from_commercial_links_audit</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Official website is an active shop/order channel; verify product availability by postal area before publishing delivery CTA.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Official website is an active shop/order channel; verify product availability by postal area before publishing delivery CTA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DL-ES-AN-SEVILLA-003-OWN_DELIVERY</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ES-AN-SEVILLA-003</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Queens Bakery Obrador</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Own delivery</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://queensbakery.es/</t>
+        </is>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>verified_from_commercial_links_audit</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Official website states orders/collection and delivery in Sevilla capital; use as direct order/info CTA.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Official website states orders/collection and delivery in Sevilla capital; use as direct order/info CTA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DL-ES-AR-ZARAGOZA-001-OWN_DELIVERY</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ES-AR-ZARAGOZA-001</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Mononoke Café</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Own delivery</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://mononokecafe.com/</t>
+        </is>
+      </c>
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>verified_from_commercial_links_audit</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Official site says pickup/order and reservation are available; exact order flow should be checked before live deep CTA.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Official site says pickup/order and reservation are available; exact order flow should be checked before live deep CTA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DL-ES-MC-LORCA-001-OWN_DELIVERY</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ES-MC-LORCA-001</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ayana Obrador</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Own delivery</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://ayanaobrador.com/</t>
+        </is>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>verified_from_commercial_links_audit</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Official website offers products for home delivery or shop pickup.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Official website offers products for home delivery or shop pickup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DL-ES-PV-BILBAO-001-OWN_DELIVERY</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ES-PV-BILBAO-001</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Bausk Kitchen</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Own delivery</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://bausk.es/</t>
+        </is>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>verified_from_commercial_links_audit</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Official website exposes PIDE BAUSK CTA; direct flow should be verified before publishing as one-click order.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Official website exposes PIDE BAUSK CTA; direct flow should be verified before publishing as one-click order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DL-ES-PV-BILBAO-002-OWN_DELIVERY</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ES-PV-BILBAO-002</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Naked &amp; Sated Bilbao</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Own delivery</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://nakedandsated.com/delivery/</t>
+        </is>
+      </c>
+      <c r="G34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>verified_from_commercial_links_audit</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Official Naked &amp; Sated delivery page; city-specific availability should be verified during app QA.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Official Naked &amp; Sated delivery page; city-specific availability should be verified during app QA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DL-ES-AN-CORDOBA-001-OWN_DELIVERY</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ES-AN-CORDOBA-001</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sana Locura Córdoba</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Own delivery</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://sanalocura.es/</t>
+        </is>
+      </c>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>verified_from_commercial_links_audit</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Official Sana Locura online shop; verify Córdoba branch pickup/delivery scope before local CTA.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Official Sana Locura online shop; verify Córdoba branch pickup/delivery scope before local CTA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DL-ES-VC-ALICANTE-001-OWN_DELIVERY</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ES-VC-ALICANTE-001</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Nonna Celia</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Own delivery</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://nonnacelia.com/</t>
+        </is>
+      </c>
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>verified_from_commercial_links_audit</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Official site exposes PEDIR CTA; use only after validating the exact order/deeplink target in app QA.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Official site exposes PEDIR CTA; use only after validating the exact order/deeplink target in app QA.</t>
         </is>
       </c>
     </row>
@@ -48597,12 +49151,12 @@
       </c>
       <c r="I3" s="29" t="inlineStr">
         <is>
-          <t>verified_official_booking_link</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J3" s="29" t="inlineStr">
         <is>
-          <t>https://tabancoamores.com/</t>
+          <t>Official site exposes Reservas page.</t>
         </is>
       </c>
       <c r="K3" s="29" t="inlineStr">
@@ -48629,7 +49183,7 @@
       </c>
       <c r="D4" s="29" t="inlineStr">
         <is>
-          <t>Reservator</t>
+          <t>Own website</t>
         </is>
       </c>
       <c r="E4" s="29" t="inlineStr">
@@ -48652,12 +49206,12 @@
       </c>
       <c r="I4" s="29" t="inlineStr">
         <is>
-          <t>verified_platform_profile</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J4" s="29" t="inlineStr">
         <is>
-          <t>https://restaurantewaraku.com/</t>
+          <t>Official site links to Reservator booking flow.</t>
         </is>
       </c>
       <c r="K4" s="29" t="inlineStr">
@@ -48707,12 +49261,12 @@
       </c>
       <c r="I5" s="29" t="inlineStr">
         <is>
-          <t>verified_official_booking_link</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J5" s="29" t="inlineStr">
         <is>
-          <t>https://nakedandsated.com/reservas/</t>
+          <t>Official reservation page covers Madrid branches.</t>
         </is>
       </c>
       <c r="K5" s="29" t="inlineStr">
@@ -48762,12 +49316,12 @@
       </c>
       <c r="I6" s="29" t="inlineStr">
         <is>
-          <t>verified_official_booking_link</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J6" s="29" t="inlineStr">
         <is>
-          <t>https://nakedandsated.com/reservas/</t>
+          <t>Official reservation page covers Madrid branches.</t>
         </is>
       </c>
       <c r="K6" s="29" t="inlineStr">
@@ -48817,12 +49371,12 @@
       </c>
       <c r="I7" s="29" t="inlineStr">
         <is>
-          <t>verified_official_booking_link</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J7" s="29" t="inlineStr">
         <is>
-          <t>https://nakedandsated.com/reservas/</t>
+          <t>Official reservation page covers Madrid branches.</t>
         </is>
       </c>
       <c r="K7" s="29" t="inlineStr">
@@ -48872,12 +49426,12 @@
       </c>
       <c r="I8" s="29" t="inlineStr">
         <is>
-          <t>verified_official_booking_link</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J8" s="29" t="inlineStr">
         <is>
-          <t>https://nakedandsated.com/reservas/</t>
+          <t>Official reservation page covers Pozuelo branch.</t>
         </is>
       </c>
       <c r="K8" s="29" t="inlineStr">
@@ -48927,12 +49481,12 @@
       </c>
       <c r="I9" s="29" t="inlineStr">
         <is>
-          <t>verified_platform_profile</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J9" s="29" t="inlineStr">
         <is>
-          <t>https://www.thefork.es/restaurante/cal-marius-449-sagrada-familia-r754276</t>
+          <t>Direct TheFork restaurant page found.</t>
         </is>
       </c>
       <c r="K9" s="29" t="inlineStr">
@@ -48982,12 +49536,12 @@
       </c>
       <c r="I10" s="29" t="inlineStr">
         <is>
-          <t>verified_official_booking_link</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J10" s="29" t="inlineStr">
         <is>
-          <t>https://arukubcn.com/provencia/</t>
+          <t>Official location page offers reservation path.</t>
         </is>
       </c>
       <c r="K10" s="29" t="inlineStr">
@@ -49037,12 +49591,12 @@
       </c>
       <c r="I11" s="29" t="inlineStr">
         <is>
-          <t>verified_official_booking_link</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J11" s="29" t="inlineStr">
         <is>
-          <t>https://arukubcn.com/</t>
+          <t>Official site offers reservation path; branch-specific booking URL not separated.</t>
         </is>
       </c>
       <c r="K11" s="29" t="inlineStr">
@@ -49092,12 +49646,12 @@
       </c>
       <c r="I12" s="29" t="inlineStr">
         <is>
-          <t>verified_official_booking_link</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J12" s="29" t="inlineStr">
         <is>
-          <t>https://nakedandsated.com/reservas/</t>
+          <t>Official reservation page for Naked &amp; Sated branches.</t>
         </is>
       </c>
       <c r="K12" s="29" t="inlineStr">
@@ -49147,12 +49701,12 @@
       </c>
       <c r="I13" s="29" t="inlineStr">
         <is>
-          <t>verified_official_booking_link</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J13" s="29" t="inlineStr">
         <is>
-          <t>https://rioluz.es/contacto/</t>
+          <t>Official contact page says reservations up to 20 people can be made via the website.</t>
         </is>
       </c>
       <c r="K13" s="29" t="inlineStr">
@@ -49202,12 +49756,12 @@
       </c>
       <c r="I14" s="29" t="inlineStr">
         <is>
-          <t>verified_official_booking_link</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J14" s="29" t="inlineStr">
         <is>
-          <t>https://nonnacelia.com/</t>
+          <t>Official site exposes RESERVAR CTA; verify final booking endpoint before publishing.</t>
         </is>
       </c>
       <c r="K14" s="29" t="inlineStr">
@@ -49257,12 +49811,12 @@
       </c>
       <c r="I15" s="29" t="inlineStr">
         <is>
-          <t>verified_official_booking_link</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J15" s="29" t="inlineStr">
         <is>
-          <t>https://mononokecafe.com/</t>
+          <t>Official site says guests can reserve for the venue; verify final booking flow before publishing.</t>
         </is>
       </c>
       <c r="K15" s="29" t="inlineStr">
@@ -49312,12 +49866,12 @@
       </c>
       <c r="I16" s="29" t="inlineStr">
         <is>
-          <t>verified_official_booking_link</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J16" s="29" t="inlineStr">
         <is>
-          <t>https://www.okashisanda.com/reservas</t>
+          <t>Official website reservation page for Malasaña.</t>
         </is>
       </c>
       <c r="K16" s="29" t="inlineStr">
@@ -49367,12 +49921,12 @@
       </c>
       <c r="I17" s="29" t="inlineStr">
         <is>
-          <t>verified_official_booking_link</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J17" s="29" t="inlineStr">
         <is>
-          <t>https://www.okashisanda.com/copia-de-reservas-malasa%C3%B1a-madrid</t>
+          <t>Official website reservation page for Lavapiés.</t>
         </is>
       </c>
       <c r="K17" s="29" t="inlineStr">
@@ -49422,12 +49976,12 @@
       </c>
       <c r="I18" s="29" t="inlineStr">
         <is>
-          <t>verified_official_booking_link</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J18" s="29" t="inlineStr">
         <is>
-          <t>https://restaurantenicontrigonisinti.com/?lang=es</t>
+          <t>Official website contains reservation section; no TheFork link was assumed.</t>
         </is>
       </c>
       <c r="K18" s="29" t="inlineStr">
@@ -49477,12 +50031,12 @@
       </c>
       <c r="I19" s="29" t="inlineStr">
         <is>
-          <t>verified_official_booking_link</t>
+          <t>verified_from_commercial_links_audit</t>
         </is>
       </c>
       <c r="J19" s="29" t="inlineStr">
         <is>
-          <t>https://www.elpalacegijon.es/reservas-el-palace-gijon</t>
+          <t>Official website reservation page.</t>
         </is>
       </c>
       <c r="K19" s="29" t="inlineStr">

--- a/data-source/CeliacSafe_Datenbank_v4_Spain_129_geocoded.xlsx
+++ b/data-source/CeliacSafe_Datenbank_v4_Spain_129_geocoded.xlsx
@@ -607,7 +607,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -622,7 +621,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -672,7 +670,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -34189,7 +34186,11 @@
       <c r="AD77" s="29" t="n"/>
       <c r="AE77" s="29" t="n"/>
       <c r="AF77" s="29" t="n"/>
-      <c r="AG77" s="29" t="n"/>
+      <c r="AG77" s="29" t="inlineStr">
+        <is>
+          <t>Official site states Okashi became the first certified Japanese restaurant 100% free of gluten and lactose and lists this Malasaña address.</t>
+        </is>
+      </c>
       <c r="AH77" s="29" t="n"/>
       <c r="AI77" s="29" t="n"/>
       <c r="AJ77" s="29" t="n"/>
@@ -34440,7 +34441,11 @@
       <c r="AD78" s="29" t="n"/>
       <c r="AE78" s="29" t="n"/>
       <c r="AF78" s="29" t="n"/>
-      <c r="AG78" s="29" t="n"/>
+      <c r="AG78" s="29" t="inlineStr">
+        <is>
+          <t>Official site states the restaurant concept is certified 100% free of gluten and lactose and lists the Lavapiés address.</t>
+        </is>
+      </c>
       <c r="AH78" s="29" t="n"/>
       <c r="AI78" s="29" t="n"/>
       <c r="AJ78" s="29" t="n"/>
@@ -34695,7 +34700,11 @@
       <c r="AD79" s="29" t="n"/>
       <c r="AE79" s="29" t="n"/>
       <c r="AF79" s="29" t="n"/>
-      <c r="AG79" s="29" t="n"/>
+      <c r="AG79" s="29" t="inlineStr">
+        <is>
+          <t>Official site confirms the 2025 move to Alcobendas and describes its gluten-free restaurant awards; specialist sources describe a 100% gluten-free menu.</t>
+        </is>
+      </c>
       <c r="AH79" s="29" t="n"/>
       <c r="AI79" s="29" t="n"/>
       <c r="AJ79" s="29" t="n"/>
@@ -34934,7 +34943,11 @@
       <c r="AD80" s="29" t="n"/>
       <c r="AE80" s="29" t="n"/>
       <c r="AF80" s="29" t="n"/>
-      <c r="AG80" s="29" t="n"/>
+      <c r="AG80" s="29" t="inlineStr">
+        <is>
+          <t>Official Carmela page invites users to try its 100% gluten-free menu; Celicidad notes this Carmela venue is one of the chain's 100% gluten-free locations.</t>
+        </is>
+      </c>
       <c r="AH80" s="29" t="n"/>
       <c r="AI80" s="29" t="n"/>
       <c r="AJ80" s="29" t="n"/>
@@ -35173,7 +35186,11 @@
       <c r="AD81" s="29" t="n"/>
       <c r="AE81" s="29" t="n"/>
       <c r="AF81" s="29" t="n"/>
-      <c r="AG81" s="29" t="n"/>
+      <c r="AG81" s="29" t="inlineStr">
+        <is>
+          <t>Official Carmela page says La Nonna Carmela is the first 100% gluten-free Italian restaurant and pizzeria in Granada; Celicidad confirms the address and 100% status.</t>
+        </is>
+      </c>
       <c r="AH81" s="29" t="n"/>
       <c r="AI81" s="29" t="n"/>
       <c r="AJ81" s="29" t="n"/>
@@ -35420,7 +35437,11 @@
       <c r="AD82" s="29" t="n"/>
       <c r="AE82" s="29" t="n"/>
       <c r="AF82" s="29" t="n"/>
-      <c r="AG82" s="29" t="n"/>
+      <c r="AG82" s="29" t="inlineStr">
+        <is>
+          <t>Official site states all dishes are suitable for celiacs and that the restaurant is completely gluten-free with annual ACEPA certification.</t>
+        </is>
+      </c>
       <c r="AH82" s="29" t="n"/>
       <c r="AI82" s="29" t="n"/>
       <c r="AJ82" s="29" t="n"/>
@@ -35667,7 +35688,11 @@
       <c r="AD83" s="29" t="n"/>
       <c r="AE83" s="29" t="n"/>
       <c r="AF83" s="29" t="n"/>
-      <c r="AG83" s="29" t="n"/>
+      <c r="AG83" s="29" t="inlineStr">
+        <is>
+          <t>Official site describes El Palace's highlighted dishes as 100% gluten-free and publishes current contact details and booking page.</t>
+        </is>
+      </c>
       <c r="AH83" s="29" t="n"/>
       <c r="AI83" s="29" t="n"/>
       <c r="AJ83" s="29" t="n"/>
@@ -35914,7 +35939,11 @@
       <c r="AD84" s="29" t="n"/>
       <c r="AE84" s="29" t="n"/>
       <c r="AF84" s="29" t="n"/>
-      <c r="AG84" s="29" t="n"/>
+      <c r="AG84" s="29" t="inlineStr">
+        <is>
+          <t>Official Instagram states 'Carta 100% sin gluten'; Celicidad/FACE-related sources describe FACE/ACECyL certification and full celiac suitability.</t>
+        </is>
+      </c>
       <c r="AH84" s="29" t="n"/>
       <c r="AI84" s="29" t="n"/>
       <c r="AJ84" s="29" t="n"/>
@@ -36157,7 +36186,11 @@
       <c r="AD85" s="29" t="n"/>
       <c r="AE85" s="29" t="n"/>
       <c r="AF85" s="29" t="n"/>
-      <c r="AG85" s="29" t="n"/>
+      <c r="AG85" s="29" t="inlineStr">
+        <is>
+          <t>Official Instagram states gluten free and FACE/ACEGA certification; specialist directories describe it as a 100% gluten-free taberna.</t>
+        </is>
+      </c>
       <c r="AH85" s="29" t="n"/>
       <c r="AI85" s="29" t="n"/>
       <c r="AJ85" s="29" t="n"/>
@@ -36400,7 +36433,11 @@
       <c r="AD86" s="29" t="n"/>
       <c r="AE86" s="29" t="n"/>
       <c r="AF86" s="29" t="n"/>
-      <c r="AG86" s="29" t="n"/>
+      <c r="AG86" s="29" t="inlineStr">
+        <is>
+          <t>Official KrümCoffee/0% Gluten locations page lists this cafeteria; the celiac association directory marks these 0% Gluten locations as 100% and as gluten-free bakery/pastry/cafeteria sites.</t>
+        </is>
+      </c>
       <c r="AH86" s="29" t="n"/>
       <c r="AI86" s="29" t="n"/>
       <c r="AJ86" s="29" t="n"/>
@@ -36643,7 +36680,11 @@
       <c r="AD87" s="29" t="n"/>
       <c r="AE87" s="29" t="n"/>
       <c r="AF87" s="29" t="n"/>
-      <c r="AG87" s="29" t="n"/>
+      <c r="AG87" s="29" t="inlineStr">
+        <is>
+          <t>Official KrümCoffee/0% Gluten locations page lists this cafeteria; the celiac association directory marks these 0% Gluten locations as 100% and as gluten-free bakery/pastry/cafeteria sites.</t>
+        </is>
+      </c>
       <c r="AH87" s="29" t="n"/>
       <c r="AI87" s="29" t="n"/>
       <c r="AJ87" s="29" t="n"/>
@@ -36882,7 +36923,11 @@
       <c r="AD88" s="29" t="n"/>
       <c r="AE88" s="29" t="n"/>
       <c r="AF88" s="29" t="n"/>
-      <c r="AG88" s="29" t="n"/>
+      <c r="AG88" s="29" t="inlineStr">
+        <is>
+          <t>Official KrümCoffee/0% Gluten locations page lists this cafeteria; the celiac association directory marks these 0% Gluten locations as 100% and as gluten-free bakery/pastry/cafeteria sites.</t>
+        </is>
+      </c>
       <c r="AH88" s="29" t="n"/>
       <c r="AI88" s="29" t="n"/>
       <c r="AJ88" s="29" t="n"/>
@@ -37125,7 +37170,11 @@
       <c r="AD89" s="29" t="n"/>
       <c r="AE89" s="29" t="n"/>
       <c r="AF89" s="29" t="n"/>
-      <c r="AG89" s="29" t="n"/>
+      <c r="AG89" s="29" t="inlineStr">
+        <is>
+          <t>Official KrümCoffee/0% Gluten locations page lists this cafeteria; the celiac association directory marks these 0% Gluten locations as 100% and as gluten-free bakery/pastry/cafeteria sites.</t>
+        </is>
+      </c>
       <c r="AH89" s="29" t="n"/>
       <c r="AI89" s="29" t="n"/>
       <c r="AJ89" s="29" t="n"/>
@@ -37368,7 +37417,11 @@
       <c r="AD90" s="29" t="n"/>
       <c r="AE90" s="29" t="n"/>
       <c r="AF90" s="29" t="n"/>
-      <c r="AG90" s="29" t="n"/>
+      <c r="AG90" s="29" t="inlineStr">
+        <is>
+          <t>Official KrümCoffee/0% Gluten locations page lists this cafeteria; the celiac association directory marks these 0% Gluten locations as 100% and as gluten-free bakery/pastry/cafeteria sites.</t>
+        </is>
+      </c>
       <c r="AH90" s="29" t="n"/>
       <c r="AI90" s="29" t="n"/>
       <c r="AJ90" s="29" t="n"/>
@@ -37611,7 +37664,11 @@
       <c r="AD91" s="29" t="n"/>
       <c r="AE91" s="29" t="n"/>
       <c r="AF91" s="29" t="n"/>
-      <c r="AG91" s="29" t="n"/>
+      <c r="AG91" s="29" t="inlineStr">
+        <is>
+          <t>Official KrümCoffee/0% Gluten locations page lists this cafeteria; the celiac association directory marks these 0% Gluten locations as 100% and as gluten-free bakery/pastry/cafeteria sites.</t>
+        </is>
+      </c>
       <c r="AH91" s="29" t="n"/>
       <c r="AI91" s="29" t="n"/>
       <c r="AJ91" s="29" t="n"/>
@@ -37846,7 +37903,11 @@
       <c r="AD92" s="29" t="n"/>
       <c r="AE92" s="29" t="n"/>
       <c r="AF92" s="29" t="n"/>
-      <c r="AG92" s="29" t="n"/>
+      <c r="AG92" s="29" t="inlineStr">
+        <is>
+          <t>Celiac association directory marks A mi panera as 100% and describes it as an own-production gluten-free and lactose-free bakery/pastry shop with tasting/café area.</t>
+        </is>
+      </c>
       <c r="AH92" s="29" t="n"/>
       <c r="AI92" s="29" t="n"/>
       <c r="AJ92" s="29" t="n"/>
@@ -38085,7 +38146,11 @@
       <c r="AD93" s="29" t="n"/>
       <c r="AE93" s="29" t="n"/>
       <c r="AF93" s="29" t="n"/>
-      <c r="AG93" s="29" t="n"/>
+      <c r="AG93" s="29" t="inlineStr">
+        <is>
+          <t>Celiac association directory marks Aborigen as 100% and states the menu is 100% gluten-free.</t>
+        </is>
+      </c>
       <c r="AH93" s="29" t="n"/>
       <c r="AI93" s="29" t="n"/>
       <c r="AJ93" s="29" t="n"/>
@@ -38324,7 +38389,11 @@
       <c r="AD94" s="29" t="n"/>
       <c r="AE94" s="29" t="n"/>
       <c r="AF94" s="29" t="n"/>
-      <c r="AG94" s="29" t="n"/>
+      <c r="AG94" s="29" t="inlineStr">
+        <is>
+          <t>Official site describes Santo Tomé Brunch as a gluten-free culinary space for celiacs and its Instagram identifies the venue as 'SIN GLUTEN'.</t>
+        </is>
+      </c>
       <c r="AH94" s="29" t="n"/>
       <c r="AI94" s="29" t="n"/>
       <c r="AJ94" s="29" t="n"/>
@@ -38559,7 +38628,11 @@
       <c r="AD95" s="29" t="n"/>
       <c r="AE95" s="29" t="n"/>
       <c r="AF95" s="29" t="n"/>
-      <c r="AG95" s="29" t="n"/>
+      <c r="AG95" s="29" t="inlineStr">
+        <is>
+          <t>Official site says the business focuses on guaranteeing that everything is gluten-free; official social content states products are 100% sin gluten.</t>
+        </is>
+      </c>
       <c r="AH95" s="29" t="n"/>
       <c r="AI95" s="29" t="n"/>
       <c r="AJ95" s="29" t="n"/>
@@ -38798,7 +38871,11 @@
       <c r="AD96" s="29" t="n"/>
       <c r="AE96" s="29" t="n"/>
       <c r="AF96" s="29" t="n"/>
-      <c r="AG96" s="29" t="n"/>
+      <c r="AG96" s="29" t="inlineStr">
+        <is>
+          <t>Official market page describes an ACECOVA-accredited space for celiacs with fresh bread and pastries, all gluten-free; official Instagram states an obrador 100% sin gluten.</t>
+        </is>
+      </c>
       <c r="AH96" s="29" t="n"/>
       <c r="AI96" s="29" t="n"/>
       <c r="AJ96" s="29" t="n"/>
@@ -39029,7 +39106,11 @@
       <c r="AD97" s="29" t="n"/>
       <c r="AE97" s="29" t="n"/>
       <c r="AF97" s="29" t="n"/>
-      <c r="AG97" s="29" t="n"/>
+      <c r="AG97" s="29" t="inlineStr">
+        <is>
+          <t>Official Instagram describes it as a safe 100% gluten-free space; Cadena SER reported it as the only 100% gluten-free bar in Cuenca province with a complete gluten-free menu.</t>
+        </is>
+      </c>
       <c r="AH97" s="29" t="n"/>
       <c r="AI97" s="29" t="n"/>
       <c r="AJ97" s="29" t="n"/>
@@ -39272,7 +39353,11 @@
       <c r="AD98" s="29" t="n"/>
       <c r="AE98" s="29" t="n"/>
       <c r="AF98" s="29" t="n"/>
-      <c r="AG98" s="29" t="n"/>
+      <c r="AG98" s="29" t="inlineStr">
+        <is>
+          <t>Official website identifies Celidulce as an obrador sin gluten and lists its Vigo address and contact details.</t>
+        </is>
+      </c>
       <c r="AH98" s="29" t="n"/>
       <c r="AI98" s="29" t="n"/>
       <c r="AJ98" s="29" t="n"/>
@@ -39511,7 +39596,11 @@
       <c r="AD99" s="29" t="n"/>
       <c r="AE99" s="29" t="n"/>
       <c r="AF99" s="29" t="n"/>
-      <c r="AG99" s="29" t="n"/>
+      <c r="AG99" s="29" t="inlineStr">
+        <is>
+          <t>Official site says Gluten Tag! is a 100% gluten-free artisan bakery; celiac association directory also marks the venue as 100%.</t>
+        </is>
+      </c>
       <c r="AH99" s="29" t="n"/>
       <c r="AI99" s="29" t="n"/>
       <c r="AJ99" s="29" t="n"/>
@@ -39758,7 +39847,11 @@
       <c r="AD100" s="29" t="n"/>
       <c r="AE100" s="29" t="n"/>
       <c r="AF100" s="29" t="n"/>
-      <c r="AG100" s="29" t="n"/>
+      <c r="AG100" s="29" t="inlineStr">
+        <is>
+          <t>Official site states Glutery sells artisan gluten-free/lactose-free products and lists this address; Catalunya celiac association lists the obrador location.</t>
+        </is>
+      </c>
       <c r="AH100" s="29" t="n"/>
       <c r="AI100" s="29" t="n"/>
       <c r="AJ100" s="29" t="n"/>
@@ -40005,7 +40098,11 @@
       <c r="AD101" s="29" t="n"/>
       <c r="AE101" s="29" t="n"/>
       <c r="AF101" s="29" t="n"/>
-      <c r="AG101" s="29" t="n"/>
+      <c r="AG101" s="29" t="inlineStr">
+        <is>
+          <t>Official site lists a second Glutery address at Provença 197 and describes the brand as always gluten-free.</t>
+        </is>
+      </c>
       <c r="AH101" s="29" t="n"/>
       <c r="AI101" s="29" t="n"/>
       <c r="AJ101" s="29" t="n"/>
@@ -40244,7 +40341,11 @@
       <c r="AD102" s="29" t="n"/>
       <c r="AE102" s="29" t="n"/>
       <c r="AF102" s="29" t="n"/>
-      <c r="AG102" s="29" t="n"/>
+      <c r="AG102" s="29" t="inlineStr">
+        <is>
+          <t>Official website describes Hanai as a vegan gluten-free pastry shop and official Instagram lists the Born address.</t>
+        </is>
+      </c>
       <c r="AH102" s="29" t="n"/>
       <c r="AI102" s="29" t="n"/>
       <c r="AJ102" s="29" t="n"/>
@@ -40483,7 +40584,11 @@
       <c r="AD103" s="29" t="n"/>
       <c r="AE103" s="29" t="n"/>
       <c r="AF103" s="29" t="n"/>
-      <c r="AG103" s="29" t="n"/>
+      <c r="AG103" s="29" t="inlineStr">
+        <is>
+          <t>Dedicated gluten-free bakery/pastry concept; specialist sources describe it as 100% sin gluten and ACIB-associated.</t>
+        </is>
+      </c>
       <c r="AH103" s="29" t="n"/>
       <c r="AI103" s="29" t="n"/>
       <c r="AJ103" s="29" t="n"/>
@@ -40730,7 +40835,11 @@
       <c r="AD104" s="29" t="n"/>
       <c r="AE104" s="29" t="n"/>
       <c r="AF104" s="29" t="n"/>
-      <c r="AG104" s="29" t="n"/>
+      <c r="AG104" s="29" t="inlineStr">
+        <is>
+          <t>Official materials describe the concept/menu as 100% vegan and gluten-free.</t>
+        </is>
+      </c>
       <c r="AH104" s="29" t="n"/>
       <c r="AI104" s="29" t="n"/>
       <c r="AJ104" s="29" t="n"/>
@@ -40965,7 +41074,11 @@
       </c>
       <c r="AE105" s="29" t="n"/>
       <c r="AF105" s="29" t="n"/>
-      <c r="AG105" s="29" t="n"/>
+      <c r="AG105" s="29" t="inlineStr">
+        <is>
+          <t>ACIB publicly states Bar Café Rico has a 100% gluten-free menu/carta; no full public menu was found, so keep source note visible.</t>
+        </is>
+      </c>
       <c r="AH105" s="29" t="n"/>
       <c r="AI105" s="29" t="n"/>
       <c r="AJ105" s="29" t="n"/>
@@ -41200,7 +41313,11 @@
       <c r="AD106" s="29" t="n"/>
       <c r="AE106" s="29" t="n"/>
       <c r="AF106" s="29" t="n"/>
-      <c r="AG106" s="29" t="n"/>
+      <c r="AG106" s="29" t="inlineStr">
+        <is>
+          <t>Official website describes a dedicated gluten-free bakery/pastry concept; association listing marks it 100%.</t>
+        </is>
+      </c>
       <c r="AH106" s="29" t="n"/>
       <c r="AI106" s="29" t="n"/>
       <c r="AJ106" s="29" t="n"/>
@@ -41439,7 +41556,11 @@
       <c r="AD107" s="29" t="n"/>
       <c r="AE107" s="29" t="n"/>
       <c r="AF107" s="29" t="n"/>
-      <c r="AG107" s="29" t="n"/>
+      <c r="AG107" s="29" t="inlineStr">
+        <is>
+          <t>Association listing marks Alatria 100% and describes it as gluten-free and other-allergen-free artisanal obrador.</t>
+        </is>
+      </c>
       <c r="AH107" s="29" t="n"/>
       <c r="AI107" s="29" t="n"/>
       <c r="AJ107" s="29" t="n"/>
@@ -41678,7 +41799,11 @@
       <c r="AD108" s="29" t="n"/>
       <c r="AE108" s="29" t="n"/>
       <c r="AF108" s="29" t="n"/>
-      <c r="AG108" s="29" t="n"/>
+      <c r="AG108" s="29" t="inlineStr">
+        <is>
+          <t>Specialist sources and official Instagram describe the obrador as 100% gluten-free.</t>
+        </is>
+      </c>
       <c r="AH108" s="29" t="n"/>
       <c r="AI108" s="29" t="n"/>
       <c r="AJ108" s="29" t="n"/>
@@ -41913,7 +42038,11 @@
       <c r="AD109" s="29" t="n"/>
       <c r="AE109" s="29" t="n"/>
       <c r="AF109" s="29" t="n"/>
-      <c r="AG109" s="29" t="n"/>
+      <c r="AG109" s="29" t="inlineStr">
+        <is>
+          <t>Updated CeliNews guide describes Amaranto as an obrador 100% sin gluten with eat-in space.</t>
+        </is>
+      </c>
       <c r="AH109" s="29" t="n"/>
       <c r="AI109" s="29" t="n"/>
       <c r="AJ109" s="29" t="n"/>
@@ -42148,7 +42277,11 @@
       <c r="AD110" s="29" t="n"/>
       <c r="AE110" s="29" t="n"/>
       <c r="AF110" s="29" t="n"/>
-      <c r="AG110" s="29" t="n"/>
+      <c r="AG110" s="29" t="inlineStr">
+        <is>
+          <t>Specialist guide lists Bensenta as a 100% gluten-free pastry shop.</t>
+        </is>
+      </c>
       <c r="AH110" s="29" t="n"/>
       <c r="AI110" s="29" t="n"/>
       <c r="AJ110" s="29" t="n"/>
@@ -42383,7 +42516,11 @@
       <c r="AD111" s="29" t="n"/>
       <c r="AE111" s="29" t="n"/>
       <c r="AF111" s="29" t="n"/>
-      <c r="AG111" s="29" t="n"/>
+      <c r="AG111" s="29" t="inlineStr">
+        <is>
+          <t>Updated CeliNews guide lists Chök A Coruña as a 100% gluten-free pastry shop.</t>
+        </is>
+      </c>
       <c r="AH111" s="29" t="n"/>
       <c r="AI111" s="29" t="n"/>
       <c r="AJ111" s="29" t="n"/>
@@ -42618,7 +42755,11 @@
       <c r="AD112" s="29" t="n"/>
       <c r="AE112" s="29" t="n"/>
       <c r="AF112" s="29" t="n"/>
-      <c r="AG112" s="29" t="n"/>
+      <c r="AG112" s="29" t="inlineStr">
+        <is>
+          <t>Updated CeliNews guide describes Esencia Restaurante Coruña as a 100% gluten-free restaurant.</t>
+        </is>
+      </c>
       <c r="AH112" s="29" t="n"/>
       <c r="AI112" s="29" t="n"/>
       <c r="AJ112" s="29" t="n"/>
@@ -42853,7 +42994,11 @@
       <c r="AD113" s="29" t="n"/>
       <c r="AE113" s="29" t="n"/>
       <c r="AF113" s="29" t="n"/>
-      <c r="AG113" s="29" t="n"/>
+      <c r="AG113" s="29" t="inlineStr">
+        <is>
+          <t>Updated CeliNews guide describes Tamarindo as a 100% gluten-free Mexican restaurant.</t>
+        </is>
+      </c>
       <c r="AH113" s="29" t="n"/>
       <c r="AI113" s="29" t="n"/>
       <c r="AJ113" s="29" t="n"/>
@@ -43088,7 +43233,11 @@
       <c r="AD114" s="29" t="n"/>
       <c r="AE114" s="29" t="n"/>
       <c r="AF114" s="29" t="n"/>
-      <c r="AG114" s="29" t="n"/>
+      <c r="AG114" s="29" t="inlineStr">
+        <is>
+          <t>Senza Glutine branch; updated CeliNews guide describes the A Coruña Grosso location as a 100% gluten-free restaurant.</t>
+        </is>
+      </c>
       <c r="AH114" s="29" t="n"/>
       <c r="AI114" s="29" t="n"/>
       <c r="AJ114" s="29" t="n"/>
@@ -43323,7 +43472,11 @@
       <c r="AD115" s="29" t="n"/>
       <c r="AE115" s="29" t="n"/>
       <c r="AF115" s="29" t="n"/>
-      <c r="AG115" s="29" t="n"/>
+      <c r="AG115" s="29" t="inlineStr">
+        <is>
+          <t>Association listing states carta 100% sin gluten; multiple specialized sources support a 100% GF sidrería concept.</t>
+        </is>
+      </c>
       <c r="AH115" s="29" t="n"/>
       <c r="AI115" s="29" t="n"/>
       <c r="AJ115" s="29" t="n"/>
@@ -43562,7 +43715,11 @@
       </c>
       <c r="AE116" s="29" t="n"/>
       <c r="AF116" s="29" t="n"/>
-      <c r="AG116" s="29" t="n"/>
+      <c r="AG116" s="29" t="inlineStr">
+        <is>
+          <t>Asociación de Celiacos listing states toda la carta es sin gluten and marks 100%.</t>
+        </is>
+      </c>
       <c r="AH116" s="29" t="n"/>
       <c r="AI116" s="29" t="n"/>
       <c r="AJ116" s="29" t="n"/>
@@ -43801,7 +43958,11 @@
       <c r="AD117" s="29" t="n"/>
       <c r="AE117" s="29" t="n"/>
       <c r="AF117" s="29" t="n"/>
-      <c r="AG117" s="29" t="n"/>
+      <c r="AG117" s="29" t="inlineStr">
+        <is>
+          <t>Restaurant is presented as a 100% gluten-free concept in current specialist/community sources; mark for future direct owner confirmation.</t>
+        </is>
+      </c>
       <c r="AH117" s="29" t="n"/>
       <c r="AI117" s="29" t="n"/>
       <c r="AJ117" s="29" t="n"/>
@@ -44040,7 +44201,11 @@
       </c>
       <c r="AE118" s="29" t="n"/>
       <c r="AF118" s="29" t="n"/>
-      <c r="AG118" s="29" t="n"/>
+      <c r="AG118" s="29" t="inlineStr">
+        <is>
+          <t>Official social profiles name the venue as 100% Sin Gluten; specialist guide also lists it as 100% gluten-free.</t>
+        </is>
+      </c>
       <c r="AH118" s="29" t="n"/>
       <c r="AI118" s="29" t="n"/>
       <c r="AJ118" s="29" t="n"/>
@@ -44283,7 +44448,11 @@
       </c>
       <c r="AE119" s="29" t="n"/>
       <c r="AF119" s="29" t="n"/>
-      <c r="AG119" s="29" t="n"/>
+      <c r="AG119" s="29" t="inlineStr">
+        <is>
+          <t>Official website says toda la carta 100% sin gluten; Facebook states 100% gluten-free and free of cross-contamination.</t>
+        </is>
+      </c>
       <c r="AH119" s="29" t="n"/>
       <c r="AI119" s="29" t="n"/>
       <c r="AJ119" s="29" t="n"/>
@@ -44522,7 +44691,11 @@
       </c>
       <c r="AE120" s="29" t="n"/>
       <c r="AF120" s="29" t="n"/>
-      <c r="AG120" s="29" t="n"/>
+      <c r="AG120" s="29" t="inlineStr">
+        <is>
+          <t>Specialist listings describe Casa Credente as Restaurante 100% Sin gluten in La Laguna.</t>
+        </is>
+      </c>
       <c r="AH120" s="29" t="n"/>
       <c r="AI120" s="29" t="n"/>
       <c r="AJ120" s="29" t="n"/>
@@ -44757,7 +44930,11 @@
       <c r="AD121" s="29" t="n"/>
       <c r="AE121" s="29" t="n"/>
       <c r="AF121" s="29" t="n"/>
-      <c r="AG121" s="29" t="n"/>
+      <c r="AG121" s="29" t="inlineStr">
+        <is>
+          <t>Specialist sources and community reviews describe it as a 100% gluten-free bakery/cafeteria.</t>
+        </is>
+      </c>
       <c r="AH121" s="29" t="n"/>
       <c r="AI121" s="29" t="n"/>
       <c r="AJ121" s="29" t="n"/>
@@ -44992,7 +45169,11 @@
       <c r="AD122" s="29" t="n"/>
       <c r="AE122" s="29" t="n"/>
       <c r="AF122" s="29" t="n"/>
-      <c r="AG122" s="29" t="n"/>
+      <c r="AG122" s="29" t="inlineStr">
+        <is>
+          <t>Association listing states Obrador 100% sin gluten.</t>
+        </is>
+      </c>
       <c r="AH122" s="29" t="n"/>
       <c r="AI122" s="29" t="n"/>
       <c r="AJ122" s="29" t="n"/>
@@ -45231,7 +45412,11 @@
       <c r="AD123" s="29" t="n"/>
       <c r="AE123" s="29" t="n"/>
       <c r="AF123" s="29" t="n"/>
-      <c r="AG123" s="29" t="n"/>
+      <c r="AG123" s="29" t="inlineStr">
+        <is>
+          <t>Association listing marks Celiex 64 as 100% and describes it as gluten-free bakery and pastry shop.</t>
+        </is>
+      </c>
       <c r="AH123" s="29" t="n"/>
       <c r="AI123" s="29" t="n"/>
       <c r="AJ123" s="29" t="n"/>
@@ -45466,7 +45651,11 @@
       <c r="AD124" s="29" t="n"/>
       <c r="AE124" s="29" t="n"/>
       <c r="AF124" s="29" t="n"/>
-      <c r="AG124" s="29" t="n"/>
+      <c r="AG124" s="29" t="inlineStr">
+        <is>
+          <t>Association listing marks Celilocos as 100% and AVALADO; describes daily gluten-free porras/churros and artisan pastry.</t>
+        </is>
+      </c>
       <c r="AH124" s="29" t="n"/>
       <c r="AI124" s="29" t="n"/>
       <c r="AJ124" s="29" t="n"/>
@@ -45701,7 +45890,11 @@
       <c r="AD125" s="29" t="n"/>
       <c r="AE125" s="29" t="n"/>
       <c r="AF125" s="29" t="n"/>
-      <c r="AG125" s="29" t="n"/>
+      <c r="AG125" s="29" t="inlineStr">
+        <is>
+          <t>Association listing marks Bambasia 100% and AVALADO; CeliNews describes it as the only 100% gluten-free obrador in Boadilla.</t>
+        </is>
+      </c>
       <c r="AH125" s="29" t="n"/>
       <c r="AI125" s="29" t="n"/>
       <c r="AJ125" s="29" t="n"/>
@@ -45940,7 +46133,11 @@
       <c r="AD126" s="29" t="n"/>
       <c r="AE126" s="29" t="n"/>
       <c r="AF126" s="29" t="n"/>
-      <c r="AG126" s="29" t="n"/>
+      <c r="AG126" s="29" t="inlineStr">
+        <is>
+          <t>Association listing marks the bakery as 100% and describes artisan gluten-free products.</t>
+        </is>
+      </c>
       <c r="AH126" s="29" t="n"/>
       <c r="AI126" s="29" t="n"/>
       <c r="AJ126" s="29" t="n"/>
@@ -46179,7 +46376,11 @@
       <c r="AD127" s="29" t="n"/>
       <c r="AE127" s="29" t="n"/>
       <c r="AF127" s="29" t="n"/>
-      <c r="AG127" s="29" t="n"/>
+      <c r="AG127" s="29" t="inlineStr">
+        <is>
+          <t>Caseríssima is a dedicated gluten-free obrador; Infoceliaco described it as 100% gluten-free and ACCLM as exclusive gluten-free obrador.</t>
+        </is>
+      </c>
       <c r="AH127" s="29" t="n"/>
       <c r="AI127" s="29" t="n"/>
       <c r="AJ127" s="29" t="n"/>
@@ -46410,7 +46611,11 @@
       <c r="AD128" s="29" t="n"/>
       <c r="AE128" s="29" t="n"/>
       <c r="AF128" s="29" t="n"/>
-      <c r="AG128" s="29" t="n"/>
+      <c r="AG128" s="29" t="inlineStr">
+        <is>
+          <t>Association listing marks Artediet as 100% and AVALADO; describes traditional gluten-free pastry with bakery products.</t>
+        </is>
+      </c>
       <c r="AH128" s="29" t="n"/>
       <c r="AI128" s="29" t="n"/>
       <c r="AJ128" s="29" t="n"/>
@@ -46649,7 +46854,11 @@
       <c r="AD129" s="29" t="n"/>
       <c r="AE129" s="29" t="n"/>
       <c r="AF129" s="29" t="n"/>
-      <c r="AG129" s="29" t="n"/>
+      <c r="AG129" s="29" t="inlineStr">
+        <is>
+          <t>Association listing marks Arttpa 100% and describes it as an obrador specialized in gluten-free bread.</t>
+        </is>
+      </c>
       <c r="AH129" s="29" t="n"/>
       <c r="AI129" s="29" t="n"/>
       <c r="AJ129" s="29" t="n"/>
@@ -46876,7 +47085,11 @@
       <c r="AD130" s="29" t="n"/>
       <c r="AE130" s="29" t="n"/>
       <c r="AF130" s="29" t="n"/>
-      <c r="AG130" s="29" t="n"/>
+      <c r="AG130" s="29" t="inlineStr">
+        <is>
+          <t>Recent local press identifies Doña Mare as Huelva province's first certified 100% gluten-free restaurant with a completely gluten-free menu.</t>
+        </is>
+      </c>
       <c r="AH130" s="29" t="n"/>
       <c r="AI130" s="29" t="n"/>
       <c r="AJ130" s="29" t="n"/>

--- a/data-source/CeliacSafe_Datenbank_v4_Spain_129_geocoded.xlsx
+++ b/data-source/CeliacSafe_Datenbank_v4_Spain_129_geocoded.xlsx
@@ -14642,7 +14642,7 @@
       <c r="AF2" s="29" t="str"/>
       <c r="AG2" s="29" t="inlineStr">
         <is>
-          <t>Restaurant mit Autorenküche und Tapas; als 100% glutenfrei und laktosefrei beschrieben.</t>
+          <t>Restaurant in Palmanova mit Tapas, mediterranen Gerichten, Fisch-/Fleischspeisen und spanisch inspirierten Klassikern.</t>
         </is>
       </c>
       <c r="AH2" s="29" t="inlineStr">
@@ -14898,7 +14898,7 @@
       <c r="AF3" s="29" t="str"/>
       <c r="AG3" s="29" t="inlineStr">
         <is>
-          <t>Gesundes Restaurant in Palma; offizieller Auftritt weist 100% glutenfrei aus.</t>
+          <t>Healthy-Restaurant/Café in Palma mit Bowls, Brunchgerichten, Salaten, herzhaften Speisen, Kuchen und Getränken.</t>
         </is>
       </c>
       <c r="AH3" s="29" t="inlineStr">
@@ -15150,7 +15150,7 @@
       <c r="AF4" s="29" t="str"/>
       <c r="AG4" s="29" t="inlineStr">
         <is>
-          <t>Italienisches Restaurant; offizieller Auftritt führt 100% glutenfreie Küche/Gerichte und diesen Standort.</t>
+          <t>Italienisches Restaurant in Palma mit Pizza, Pasta, Antipasti und weiteren mediterranen Gerichten.</t>
         </is>
       </c>
       <c r="AH4" s="29" t="inlineStr">
@@ -15402,7 +15402,7 @@
       <c r="AF5" s="29" t="str"/>
       <c r="AG5" s="29" t="inlineStr">
         <is>
-          <t>Italienisches Restaurant an der Playa de Palma; offizieller Auftritt führt 100% glutenfreie Küche/Gerichte und diesen Standort.</t>
+          <t>Italienisches Restaurant in Palma mit Pizza, Pasta, Antipasti und weiteren mediterranen Gerichten.</t>
         </is>
       </c>
       <c r="AH5" s="29" t="inlineStr">
@@ -15658,7 +15658,7 @@
       <c r="AF6" s="29" t="str"/>
       <c r="AG6" s="29" t="inlineStr">
         <is>
-          <t>Handwerkliche 100%-glutenfreie Bäckerei/Konditorei in Palma.</t>
+          <t>Bäckerei/Patisserie in Palma mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH6" s="29" t="inlineStr">
@@ -15910,7 +15910,7 @@
       <c r="AF7" s="29" t="str"/>
       <c r="AG7" s="29" t="inlineStr">
         <is>
-          <t>Patisserie/Obrador in Palma; alle Produkte werden als 100% glutenfrei beschrieben.</t>
+          <t>Bäckerei/Patisserie in Palma mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH7" s="29" t="inlineStr">
@@ -16166,7 +16166,7 @@
       <c r="AF8" s="29" t="str"/>
       <c r="AG8" s="29" t="inlineStr">
         <is>
-          <t>Handwerkliche glutenfreie Bäckerei/Konditorei in Palma.</t>
+          <t>Bäckerei/Patisserie in Palma mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH8" s="29" t="inlineStr">
@@ -16422,7 +16422,7 @@
       <c r="AF9" s="29" t="str"/>
       <c r="AG9" s="29" t="inlineStr">
         <is>
-          <t>100%-glutenfreies Konzept in Porto Cristo mit mallorquinischen und mediterranen Speisen.</t>
+          <t>Restaurant/Bistro in Porto Cristo mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH9" s="29" t="inlineStr">
@@ -16670,7 +16670,7 @@
       <c r="AF10" s="29" t="str"/>
       <c r="AG10" s="29" t="inlineStr">
         <is>
-          <t>Café/Obrador in Palma; offizielles Instagram beschreibt den Betrieb als 100% glutenfrei.</t>
+          <t>Bäckerei/Patisserie in Palma mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH10" s="29" t="inlineStr">
@@ -16922,7 +16922,7 @@
       <c r="AF11" s="29" t="str"/>
       <c r="AG11" s="29" t="inlineStr">
         <is>
-          <t>Glutenfreie Bäckerei/Konditorei in Pollença mit Fokus auf sichere Produkte für Zöliakie-Betroffene.</t>
+          <t>Bäckerei/Patisserie in Pollença mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH11" s="29" t="inlineStr">
@@ -17178,7 +17178,7 @@
       <c r="AF12" s="29" t="str"/>
       <c r="AG12" s="29" t="inlineStr">
         <is>
-          <t>Take-away mit hausgemachter glutenfreier Küche in Palma; in spezialisierten Quellen als 100% glutenfrei geführt.</t>
+          <t>Take-away-Konzept in Palma mit vorbereiteten Speisen, Snacks, Backwaren und Gerichten zum Mitnehmen.</t>
         </is>
       </c>
       <c r="AH12" s="29" t="inlineStr">
@@ -17430,7 +17430,7 @@
       <c r="AF13" s="29" t="str"/>
       <c r="AG13" s="29" t="inlineStr">
         <is>
-          <t>Restaurant in Maó mit 100%-glutenfreien Degustationsmenüs und Speisen.</t>
+          <t>Restaurant/Bistro in Maó mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH13" s="29" t="inlineStr">
@@ -17686,7 +17686,7 @@
       <c r="AF14" s="29" t="str"/>
       <c r="AG14" s="29" t="inlineStr">
         <is>
-          <t>Glutenfreie Pastisseria in Ferreries; der offizielle Auftritt sagt, dass ausschließlich glutenfreie Produkte hergestellt werden.</t>
+          <t>Bäckerei/Patisserie in Ferreries mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH14" s="29" t="inlineStr">
@@ -17942,7 +17942,7 @@
       <c r="AF15" s="29" t="str"/>
       <c r="AG15" s="29" t="inlineStr">
         <is>
-          <t>Glutenfreie Pastisseria im Claustre del Carme in Maó; der offizielle Auftritt sagt, dass ausschließlich glutenfreie Produkte hergestellt werden.</t>
+          <t>Bäckerei/Patisserie in Maó mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH15" s="29" t="inlineStr">
@@ -18194,7 +18194,7 @@
       <c r="AF16" s="29" t="str"/>
       <c r="AG16" s="29" t="inlineStr">
         <is>
-          <t>Healthy Bakery in Ibiza; offizielle Social-Kanäle beschreiben den Obrador als 100% glutenfrei.</t>
+          <t>Bäckerei/Patisserie in Ibiza mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH16" s="29" t="inlineStr">
@@ -18442,7 +18442,7 @@
       <c r="AF17" s="29" t="str"/>
       <c r="AG17" s="29" t="inlineStr">
         <is>
-          <t>100% veganer und glutenfreier Obrador in Santa Eulària.</t>
+          <t>Veganes bzw. plant-based Café/Restaurant in Santa Eulària des Riu mit Bowls, Kuchen, Frühstücksgerichten, Snacks und kreativer pflanzlicher Küche.</t>
         </is>
       </c>
       <c r="AH17" s="29" t="inlineStr">
@@ -18694,7 +18694,7 @@
       <c r="AF18" s="29" t="str"/>
       <c r="AG18" s="29" t="inlineStr">
         <is>
-          <t>Plant-based Restaurant in Santa Gertrudis; spezialisierte Quellen beschreiben alle Gerichte als vollständig glutenfrei.</t>
+          <t>Veganes bzw. plant-based Café/Restaurant in Santa Gertrudis de Fruitera mit Bowls, Kuchen, Frühstücksgerichten, Snacks und kreativer pflanzlicher Küche.</t>
         </is>
       </c>
       <c r="AH18" s="29" t="inlineStr">
@@ -18954,7 +18954,7 @@
       <c r="AF19" s="29" t="n"/>
       <c r="AG19" s="29" t="inlineStr">
         <is>
-          <t>Andalusisch inspirierter Tabanco in Madrid; offizieller Auftritt bezeichnet den Betrieb als 100% sin gluten.</t>
+          <t>Restaurant in Madrid mit Tapas, mediterranen Gerichten, Fisch-/Fleischspeisen und spanisch inspirierten Klassikern.</t>
         </is>
       </c>
       <c r="AH19" s="29" t="inlineStr">
@@ -19229,7 +19229,7 @@
       <c r="AF20" s="29" t="n"/>
       <c r="AG20" s="29" t="inlineStr">
         <is>
-          <t>Japanisches Restaurant in Argüelles; offizielle Website beschreibt das Konzept als 100% sin gluten.</t>
+          <t>Japanisches Restaurant in Madrid mit Sushi, warmen japanischen Gerichten, Reisgerichten und Desserts.</t>
         </is>
       </c>
       <c r="AH20" s="29" t="inlineStr">
@@ -19500,7 +19500,7 @@
       <c r="AF21" s="29" t="n"/>
       <c r="AG21" s="29" t="inlineStr">
         <is>
-          <t>Spanische Küche in Huertas; Verband bestätigt, dass die gesamte Karte glutenfrei ist.</t>
+          <t>Restaurant in Madrid mit Tapas, mediterranen Gerichten, Fisch-/Fleischspeisen und spanisch inspirierten Klassikern.</t>
         </is>
       </c>
       <c r="AH21" s="29" t="inlineStr">
@@ -19767,7 +19767,7 @@
       <c r="AF22" s="29" t="n"/>
       <c r="AG22" s="29" t="inlineStr">
         <is>
-          <t>Craft-beer-Restaurant in Villaviciosa de Odón; Website und Verband bestätigen eine 100%-glutenfreie Karte.</t>
+          <t>Restaurant/Bistro in Villaviciosa de Odón mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH22" s="29" t="inlineStr">
@@ -20030,7 +20030,7 @@
       <c r="AF23" s="29" t="n"/>
       <c r="AG23" s="29" t="inlineStr">
         <is>
-          <t>Glutenfreie Bäckerei in Retiro mit offizieller Kommunikation als Sin-Gluten-Konzept.</t>
+          <t>Bäckerei/Patisserie in Madrid mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH23" s="29" t="inlineStr">
@@ -20301,7 +20301,7 @@
       <c r="AF24" s="29" t="n"/>
       <c r="AG24" s="29" t="inlineStr">
         <is>
-          <t>Handwerkliche glutenfreie Bäckerei/Pastelería in Madrid Centro.</t>
+          <t>Bäckerei/Patisserie in Madrid mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH24" s="29" t="inlineStr">
@@ -20568,7 +20568,7 @@
       <c r="AF25" s="29" t="n"/>
       <c r="AG25" s="29" t="inlineStr">
         <is>
-          <t>Zweiter Madrider Sana-Locura-Standort; vom Verband als 100% avalado gelistet.</t>
+          <t>Bäckerei/Patisserie in Madrid mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH25" s="29" t="inlineStr">
@@ -20831,7 +20831,7 @@
       <c r="AF26" s="29" t="n"/>
       <c r="AG26" s="29" t="inlineStr">
         <is>
-          <t>Traditionsreiche Madrider Pastelería mit eigener glutenfreier Linie; Verband bestätigt 100% avalado.</t>
+          <t>Bäckerei/Patisserie in Madrid mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH26" s="29" t="inlineStr">
@@ -21094,7 +21094,7 @@
       <c r="AF27" s="29" t="n"/>
       <c r="AG27" s="29" t="inlineStr">
         <is>
-          <t>Croquetería mit vollständig glutenfreien Croquetas; neuer Verbandsvertrag listet den Standort.</t>
+          <t>Croquetería in Madrid mit verschiedenen Croquetas, kleinen herzhaften Gerichten und Take-away-Angebot.</t>
         </is>
       </c>
       <c r="AH27" s="29" t="inlineStr">
@@ -21357,7 +21357,7 @@
       <c r="AF28" s="29" t="n"/>
       <c r="AG28" s="29" t="inlineStr">
         <is>
-          <t>Zweiter Madrider Solo-de-Croquetas-Standort; Verband listet ihn im 100%-sin-gluten-Kontext.</t>
+          <t>Croquetería in Madrid mit verschiedenen Croquetas, kleinen herzhaften Gerichten und Take-away-Angebot.</t>
         </is>
       </c>
       <c r="AH28" s="29" t="inlineStr">
@@ -21632,7 +21632,7 @@
       <c r="AF29" s="29" t="n"/>
       <c r="AG29" s="29" t="inlineStr">
         <is>
-          <t>Senza-Glutine-Standort der Kette in Madrid Salamanca.</t>
+          <t>Italienisches Restaurant in Madrid mit Pizza, Pasta, Antipasti und weiteren mediterranen Gerichten.</t>
         </is>
       </c>
       <c r="AH29" s="29" t="inlineStr">
@@ -21899,7 +21899,7 @@
       <c r="AF30" s="29" t="n"/>
       <c r="AG30" s="29" t="inlineStr">
         <is>
-          <t>Senza-Glutine-Standort der Kette im Zentrum von Madrid.</t>
+          <t>Italienisches Restaurant in Madrid mit Pizza, Pasta, Antipasti und weiteren mediterranen Gerichten.</t>
         </is>
       </c>
       <c r="AH30" s="29" t="inlineStr">
@@ -22174,7 +22174,7 @@
       <c r="AF31" s="29" t="n"/>
       <c r="AG31" s="29" t="inlineStr">
         <is>
-          <t>Burgerrestaurant in Chamberí mit offizieller Aussage als glutenfreier Raum.</t>
+          <t>Burgerrestaurant in Madrid mit Burgern, Beilagen, Saucen und Casual-Food-Gerichten.</t>
         </is>
       </c>
       <c r="AH31" s="29" t="inlineStr">
@@ -22453,7 +22453,7 @@
       <c r="AF32" s="29" t="n"/>
       <c r="AG32" s="29" t="inlineStr">
         <is>
-          <t>Healthy-Restaurant der 100%-sin-gluten-Kette in Serrano.</t>
+          <t>Healthy-Restaurant/Café in Madrid mit Bowls, Brunchgerichten, Salaten, herzhaften Speisen, Kuchen und Getränken.</t>
         </is>
       </c>
       <c r="AH32" s="29" t="inlineStr">
@@ -22736,7 +22736,7 @@
       <c r="AF33" s="29" t="n"/>
       <c r="AG33" s="29" t="inlineStr">
         <is>
-          <t>Healthy-Restaurant der 100%-sin-gluten-Kette bei Preciados.</t>
+          <t>Healthy-Restaurant/Café in Madrid mit Bowls, Brunchgerichten, Salaten, herzhaften Speisen, Kuchen und Getränken.</t>
         </is>
       </c>
       <c r="AH33" s="29" t="inlineStr">
@@ -23015,7 +23015,7 @@
       <c r="AF34" s="29" t="n"/>
       <c r="AG34" s="29" t="inlineStr">
         <is>
-          <t>Healthy-Restaurant der 100%-sin-gluten-Kette bei Cuzco.</t>
+          <t>Healthy-Restaurant/Café in Madrid mit Bowls, Brunchgerichten, Salaten, herzhaften Speisen, Kuchen und Getränken.</t>
         </is>
       </c>
       <c r="AH34" s="29" t="inlineStr">
@@ -23294,7 +23294,7 @@
       <c r="AF35" s="29" t="n"/>
       <c r="AG35" s="29" t="inlineStr">
         <is>
-          <t>Healthy-Restaurant der 100%-sin-gluten-Kette in Pozuelo.</t>
+          <t>Healthy-Restaurant/Café in Pozuelo de Alarcón mit Bowls, Brunchgerichten, Salaten, herzhaften Speisen, Kuchen und Getränken.</t>
         </is>
       </c>
       <c r="AH35" s="29" t="inlineStr">
@@ -23569,7 +23569,7 @@
       <c r="AF36" s="29" t="n"/>
       <c r="AG36" s="29" t="inlineStr">
         <is>
-          <t>Restaurant im Raval; offizieller Auftritt beschreibt ein 100%-glutenfreies Erlebnis.</t>
+          <t>Restaurant/Bistro in Barcelona mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH36" s="29" t="inlineStr">
@@ -23836,7 +23836,7 @@
       <c r="AF37" s="29" t="n"/>
       <c r="AG37" s="29" t="inlineStr">
         <is>
-          <t>Restaurant nahe Sagrada Família; Website verweist auf glutenfreie/laktosefreie Speisen und offizielle Akkreditierung.</t>
+          <t>Restaurant/Bistro in Barcelona mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH37" s="29" t="inlineStr">
@@ -24119,7 +24119,7 @@
       <c r="AF38" s="29" t="n"/>
       <c r="AG38" s="29" t="inlineStr">
         <is>
-          <t>Senza-Glutine-Pizzeria der Kette in Barcelonas Eixample.</t>
+          <t>Italienisches Restaurant in Barcelona mit Pizza, Pasta, Antipasti und weiteren mediterranen Gerichten.</t>
         </is>
       </c>
       <c r="AH38" s="29" t="inlineStr">
@@ -24394,7 +24394,7 @@
       <c r="AF39" s="29" t="n"/>
       <c r="AG39" s="29" t="inlineStr">
         <is>
-          <t>Asiatisches Restaurant in Eixample; offizielles Instagram nennt Gluten Free ohne Kreuzkontamination.</t>
+          <t>Restaurant/Bistro in Barcelona mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH39" s="29" t="inlineStr">
@@ -24669,7 +24669,7 @@
       <c r="AF40" s="29" t="n"/>
       <c r="AG40" s="29" t="inlineStr">
         <is>
-          <t>Asiatisches Restaurant in Gràcia; offizielles Instagram nennt Gluten Free ohne Kreuzkontamination.</t>
+          <t>Restaurant/Bistro in Barcelona mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH40" s="29" t="inlineStr">
@@ -24948,7 +24948,7 @@
       <c r="AF41" s="29" t="n"/>
       <c r="AG41" s="29" t="inlineStr">
         <is>
-          <t>Italienisches Restaurant in Gràcia; offizielle Website sagt 100% sin gluten und frei von Kreuzkontamination.</t>
+          <t>Italienisches Restaurant in Barcelona mit Pizza, Pasta, Antipasti und weiteren mediterranen Gerichten.</t>
         </is>
       </c>
       <c r="AH41" s="29" t="inlineStr">
@@ -25219,7 +25219,7 @@
       <c r="AF42" s="29" t="n"/>
       <c r="AG42" s="29" t="inlineStr">
         <is>
-          <t>Italienisches Restaurant in Muntaner; offizieller Auftritt der Marke ist 100% sin gluten.</t>
+          <t>Italienisches Restaurant in Barcelona mit Pizza, Pasta, Antipasti und weiteren mediterranen Gerichten.</t>
         </is>
       </c>
       <c r="AH42" s="29" t="inlineStr">
@@ -25482,7 +25482,7 @@
       <c r="AF43" s="29" t="n"/>
       <c r="AG43" s="29" t="inlineStr">
         <is>
-          <t>Mexikanisches Restaurant; Website sagt, die gesamte Karte ist komplett glutenfrei und zertifiziert.</t>
+          <t>Mexikanisches Restaurant in Barcelona mit Tacos, Nachos, Salsas, Bowls und weiteren mexikanischen Klassikern.</t>
         </is>
       </c>
       <c r="AH43" s="29" t="inlineStr">
@@ -25753,7 +25753,7 @@
       <c r="AF44" s="29" t="n"/>
       <c r="AG44" s="29" t="inlineStr">
         <is>
-          <t>100%-glutenfreier Brunch-Standort nahe Sagrada Família.</t>
+          <t>Café in Barcelona mit Kaffee, Frühstück, Kuchen, Gebäck, Brunchgerichten und kleinen Speisen.</t>
         </is>
       </c>
       <c r="AH44" s="29" t="inlineStr">
@@ -26024,7 +26024,7 @@
       <c r="AF45" s="29" t="n"/>
       <c r="AG45" s="29" t="inlineStr">
         <is>
-          <t>100%-glutenfreier Brunch-Standort im Gotischen Viertel.</t>
+          <t>Café in Barcelona mit Kaffee, Frühstück, Kuchen, Gebäck, Brunchgerichten und kleinen Speisen.</t>
         </is>
       </c>
       <c r="AH45" s="29" t="inlineStr">
@@ -26295,7 +26295,7 @@
       <c r="AF46" s="29" t="n"/>
       <c r="AG46" s="29" t="inlineStr">
         <is>
-          <t>100%-glutenfreier Brunch-Standort im Eixample.</t>
+          <t>Café in Barcelona mit Kaffee, Frühstück, Kuchen, Gebäck, Brunchgerichten und kleinen Speisen.</t>
         </is>
       </c>
       <c r="AH46" s="29" t="inlineStr">
@@ -26562,7 +26562,7 @@
       <c r="AF47" s="29" t="n"/>
       <c r="AG47" s="29" t="inlineStr">
         <is>
-          <t>Gluten Free Lab/Obrador in Barcelona mit exklusiv glutenfreier Produktion.</t>
+          <t>Bäckerei/Patisserie in Barcelona mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH47" s="29" t="inlineStr">
@@ -26825,7 +26825,7 @@
       <c r="AF48" s="29" t="n"/>
       <c r="AG48" s="29" t="inlineStr">
         <is>
-          <t>Restaurant 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Restaurant/Bistro in Valencia mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH48" s="29" t="inlineStr">
@@ -27076,7 +27076,7 @@
       <c r="AF49" s="29" t="n"/>
       <c r="AG49" s="29" t="inlineStr">
         <is>
-          <t>Restaurant 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Restaurant/Bistro in Valencia mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH49" s="29" t="inlineStr">
@@ -27323,7 +27323,7 @@
       <c r="AF50" s="29" t="n"/>
       <c r="AG50" s="29" t="inlineStr">
         <is>
-          <t>Café 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Café in Valencia mit Kaffee, Frühstück, Kuchen, Gebäck, Brunchgerichten und kleinen Speisen.</t>
         </is>
       </c>
       <c r="AH50" s="29" t="inlineStr">
@@ -27574,7 +27574,7 @@
       <c r="AF51" s="29" t="n"/>
       <c r="AG51" s="29" t="inlineStr">
         <is>
-          <t>Bakery 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Bäckerei/Patisserie in Valencia mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH51" s="29" t="inlineStr">
@@ -27837,7 +27837,7 @@
       <c r="AF52" s="29" t="n"/>
       <c r="AG52" s="29" t="inlineStr">
         <is>
-          <t>Restaurant 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Restaurant in Sevilla mit Tapas, mediterranen Gerichten, Fisch-/Fleischspeisen und spanisch inspirierten Klassikern.</t>
         </is>
       </c>
       <c r="AH52" s="29" t="inlineStr">
@@ -28092,7 +28092,7 @@
       <c r="AF53" s="29" t="n"/>
       <c r="AG53" s="29" t="inlineStr">
         <is>
-          <t>Café 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Café in Sevilla mit Kaffee, Frühstück, Kuchen, Gebäck, Brunchgerichten und kleinen Speisen.</t>
         </is>
       </c>
       <c r="AH53" s="29" t="inlineStr">
@@ -28347,7 +28347,7 @@
       <c r="AF54" s="29" t="n"/>
       <c r="AG54" s="29" t="inlineStr">
         <is>
-          <t>Bakery 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Bäckerei/Patisserie in Sevilla mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH54" s="29" t="inlineStr">
@@ -28598,7 +28598,7 @@
       <c r="AF55" s="29" t="n"/>
       <c r="AG55" s="29" t="inlineStr">
         <is>
-          <t>Restaurant 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Restaurant/Bistro in Sevilla mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH55" s="29" t="inlineStr">
@@ -28857,7 +28857,7 @@
       <c r="AF56" s="29" t="n"/>
       <c r="AG56" s="29" t="inlineStr">
         <is>
-          <t>Pizzeria 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Pizzeria in Zaragoza mit Pizza, herzhaften Ofengerichten und italienisch inspirierten Speisen.</t>
         </is>
       </c>
       <c r="AH56" s="29" t="inlineStr">
@@ -29116,7 +29116,7 @@
       <c r="AF57" s="29" t="n"/>
       <c r="AG57" s="29" t="inlineStr">
         <is>
-          <t>Restaurant 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Restaurant/Bistro in Zaragoza mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH57" s="29" t="inlineStr">
@@ -29367,7 +29367,7 @@
       <c r="AF58" s="29" t="n"/>
       <c r="AG58" s="29" t="inlineStr">
         <is>
-          <t>Restaurant 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Restaurant/Bistro in Zaragoza mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH58" s="29" t="inlineStr">
@@ -29618,7 +29618,7 @@
       <c r="AF59" s="29" t="n"/>
       <c r="AG59" s="29" t="inlineStr">
         <is>
-          <t>Pastry shop 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Bäckerei/Patisserie in Málaga mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH59" s="29" t="inlineStr">
@@ -29865,7 +29865,7 @@
       <c r="AF60" s="29" t="n"/>
       <c r="AG60" s="29" t="inlineStr">
         <is>
-          <t>Restaurant 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Restaurant/Bistro in Málaga mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH60" s="29" t="inlineStr">
@@ -30120,7 +30120,7 @@
       <c r="AF61" s="29" t="n"/>
       <c r="AG61" s="29" t="inlineStr">
         <is>
-          <t>Bakery 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Bäckerei/Patisserie in Murcia mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH61" s="29" t="inlineStr">
@@ -30371,7 +30371,7 @@
       <c r="AF62" s="29" t="n"/>
       <c r="AG62" s="29" t="inlineStr">
         <is>
-          <t>Bakery 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Bäckerei/Patisserie in Murcia mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH62" s="29" t="inlineStr">
@@ -30626,7 +30626,7 @@
       <c r="AF63" s="29" t="n"/>
       <c r="AG63" s="29" t="inlineStr">
         <is>
-          <t>Bakery 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Bäckerei/Patisserie in Lorca mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH63" s="29" t="inlineStr">
@@ -30885,7 +30885,7 @@
       <c r="AF64" s="29" t="n"/>
       <c r="AG64" s="29" t="inlineStr">
         <is>
-          <t>Bakery 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Bäckerei/Patisserie in Cartagena mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH64" s="29" t="inlineStr">
@@ -31140,7 +31140,7 @@
       <c r="AF65" s="29" t="n"/>
       <c r="AG65" s="29" t="inlineStr">
         <is>
-          <t>Restaurant 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Restaurant/Bistro in Las Palmas de Gran Canaria mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH65" s="29" t="inlineStr">
@@ -31395,7 +31395,7 @@
       <c r="AF66" s="29" t="n"/>
       <c r="AG66" s="29" t="inlineStr">
         <is>
-          <t>Restaurant 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Restaurant/Bistro in Bilbao mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH66" s="29" t="inlineStr">
@@ -31650,7 +31650,7 @@
       <c r="AF67" s="29" t="n"/>
       <c r="AG67" s="29" t="inlineStr">
         <is>
-          <t>Restaurant 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Healthy-Restaurant/Café in Bilbao mit Bowls, Brunchgerichten, Salaten, herzhaften Speisen, Kuchen und Getränken.</t>
         </is>
       </c>
       <c r="AH67" s="29" t="inlineStr">
@@ -31909,7 +31909,7 @@
       <c r="AF68" s="29" t="n"/>
       <c r="AG68" s="29" t="inlineStr">
         <is>
-          <t>Bakery 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Bäckerei/Patisserie in Bilbao mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH68" s="29" t="inlineStr">
@@ -32168,7 +32168,7 @@
       <c r="AF69" s="29" t="n"/>
       <c r="AG69" s="29" t="inlineStr">
         <is>
-          <t>Restaurant 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Restaurant/Bistro in Alicante mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH69" s="29" t="inlineStr">
@@ -32423,7 +32423,7 @@
       <c r="AF70" s="29" t="n"/>
       <c r="AG70" s="29" t="inlineStr">
         <is>
-          <t>Bakery 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Bäckerei/Patisserie in Alicante mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH70" s="29" t="inlineStr">
@@ -32670,7 +32670,7 @@
       <c r="AF71" s="29" t="n"/>
       <c r="AG71" s="29" t="inlineStr">
         <is>
-          <t>Bakery 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Bäckerei/Patisserie in Alicante mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH71" s="29" t="inlineStr">
@@ -32917,7 +32917,7 @@
       <c r="AF72" s="29" t="n"/>
       <c r="AG72" s="29" t="inlineStr">
         <is>
-          <t>Bakery 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Bäckerei/Patisserie in Córdoba mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH72" s="29" t="inlineStr">
@@ -33164,7 +33164,7 @@
       <c r="AF73" s="29" t="n"/>
       <c r="AG73" s="29" t="inlineStr">
         <is>
-          <t>Bakery 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Bäckerei/Patisserie in Córdoba mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH73" s="29" t="inlineStr">
@@ -33411,7 +33411,7 @@
       <c r="AF74" s="29" t="n"/>
       <c r="AG74" s="29" t="inlineStr">
         <is>
-          <t>Restaurant 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Restaurant/Bistro in Córdoba mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH74" s="29" t="inlineStr">
@@ -33670,7 +33670,7 @@
       <c r="AF75" s="29" t="n"/>
       <c r="AG75" s="29" t="inlineStr">
         <is>
-          <t>Restaurant 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Restaurant/Bistro in Valladolid mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH75" s="29" t="inlineStr">
@@ -33925,7 +33925,7 @@
       <c r="AF76" s="29" t="n"/>
       <c r="AG76" s="29" t="inlineStr">
         <is>
-          <t>Bakery 100% glutenfrei verifiziert; nur aufgenommen wegen klarer 100%-Nachweise.</t>
+          <t>Bäckerei/Patisserie in Valladolid mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH76" s="29" t="inlineStr">
@@ -34188,7 +34188,7 @@
       <c r="AF77" s="29" t="n"/>
       <c r="AG77" s="29" t="inlineStr">
         <is>
-          <t>Official site states Okashi became the first certified Japanese restaurant 100% free of gluten and lactose and lists this Malasaña address.</t>
+          <t>Japanisches Restaurant in Madrid mit Sushi, warmen japanischen Gerichten, Reisgerichten und Desserts.</t>
         </is>
       </c>
       <c r="AH77" s="29" t="n"/>
@@ -34443,7 +34443,7 @@
       <c r="AF78" s="29" t="n"/>
       <c r="AG78" s="29" t="inlineStr">
         <is>
-          <t>Official site states the restaurant concept is certified 100% free of gluten and lactose and lists the Lavapiés address.</t>
+          <t>Japanisches Restaurant in Madrid mit Sushi, warmen japanischen Gerichten, Reisgerichten und Desserts.</t>
         </is>
       </c>
       <c r="AH78" s="29" t="n"/>
@@ -34702,7 +34702,7 @@
       <c r="AF79" s="29" t="n"/>
       <c r="AG79" s="29" t="inlineStr">
         <is>
-          <t>Official site confirms the 2025 move to Alcobendas and describes its gluten-free restaurant awards; specialist sources describe a 100% gluten-free menu.</t>
+          <t>Restaurant/Bistro in Alcobendas mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH79" s="29" t="n"/>
@@ -34945,7 +34945,7 @@
       <c r="AF80" s="29" t="n"/>
       <c r="AG80" s="29" t="inlineStr">
         <is>
-          <t>Official Carmela page invites users to try its 100% gluten-free menu; Celicidad notes this Carmela venue is one of the chain's 100% gluten-free locations.</t>
+          <t>Restaurant in Granada mit regionaler Küche, Hauptgerichten, Vorspeisen, Desserts und saisonalen Speisen.</t>
         </is>
       </c>
       <c r="AH80" s="29" t="n"/>
@@ -35188,7 +35188,7 @@
       <c r="AF81" s="29" t="n"/>
       <c r="AG81" s="29" t="inlineStr">
         <is>
-          <t>Official Carmela page says La Nonna Carmela is the first 100% gluten-free Italian restaurant and pizzeria in Granada; Celicidad confirms the address and 100% status.</t>
+          <t>Italienisches Restaurant in Granada mit Pizza, Pasta, Antipasti und weiteren mediterranen Gerichten.</t>
         </is>
       </c>
       <c r="AH81" s="29" t="n"/>
@@ -35439,7 +35439,7 @@
       <c r="AF82" s="29" t="n"/>
       <c r="AG82" s="29" t="inlineStr">
         <is>
-          <t>Official site states all dishes are suitable for celiacs and that the restaurant is completely gluten-free with annual ACEPA certification.</t>
+          <t>Restaurant in Oviedo mit Tapas, mediterranen Gerichten, Fisch-/Fleischspeisen und spanisch inspirierten Klassikern.</t>
         </is>
       </c>
       <c r="AH82" s="29" t="n"/>
@@ -35690,7 +35690,7 @@
       <c r="AF83" s="29" t="n"/>
       <c r="AG83" s="29" t="inlineStr">
         <is>
-          <t>Official site describes El Palace's highlighted dishes as 100% gluten-free and publishes current contact details and booking page.</t>
+          <t>Restaurant in Gijón mit regionaler Küche, Hauptgerichten, Vorspeisen, Desserts und saisonalen Speisen.</t>
         </is>
       </c>
       <c r="AH83" s="29" t="n"/>
@@ -35941,7 +35941,7 @@
       <c r="AF84" s="29" t="n"/>
       <c r="AG84" s="29" t="inlineStr">
         <is>
-          <t>Official Instagram states 'Carta 100% sin gluten'; Celicidad/FACE-related sources describe FACE/ACECyL certification and full celiac suitability.</t>
+          <t>Restaurant in Zamora mit regionaler Küche, Hauptgerichten, Vorspeisen, Desserts und saisonalen Speisen.</t>
         </is>
       </c>
       <c r="AH84" s="29" t="n"/>
@@ -36188,7 +36188,7 @@
       <c r="AF85" s="29" t="n"/>
       <c r="AG85" s="29" t="inlineStr">
         <is>
-          <t>Official Instagram states gluten free and FACE/ACEGA certification; specialist directories describe it as a 100% gluten-free taberna.</t>
+          <t>Restaurant/Bistro in A Coruña mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH85" s="29" t="n"/>
@@ -36435,7 +36435,7 @@
       <c r="AF86" s="29" t="n"/>
       <c r="AG86" s="29" t="inlineStr">
         <is>
-          <t>Official KrümCoffee/0% Gluten locations page lists this cafeteria; the celiac association directory marks these 0% Gluten locations as 100% and as gluten-free bakery/pastry/cafeteria sites.</t>
+          <t>Bäckerei/Patisserie in Granollers mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH86" s="29" t="n"/>
@@ -36682,7 +36682,7 @@
       <c r="AF87" s="29" t="n"/>
       <c r="AG87" s="29" t="inlineStr">
         <is>
-          <t>Official KrümCoffee/0% Gluten locations page lists this cafeteria; the celiac association directory marks these 0% Gluten locations as 100% and as gluten-free bakery/pastry/cafeteria sites.</t>
+          <t>Bäckerei/Patisserie in Sant Cugat del Vallès mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH87" s="29" t="n"/>
@@ -36925,7 +36925,7 @@
       <c r="AF88" s="29" t="n"/>
       <c r="AG88" s="29" t="inlineStr">
         <is>
-          <t>Official KrümCoffee/0% Gluten locations page lists this cafeteria; the celiac association directory marks these 0% Gluten locations as 100% and as gluten-free bakery/pastry/cafeteria sites.</t>
+          <t>Bäckerei/Patisserie in Sabadell mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH88" s="29" t="n"/>
@@ -37172,7 +37172,7 @@
       <c r="AF89" s="29" t="n"/>
       <c r="AG89" s="29" t="inlineStr">
         <is>
-          <t>Official KrümCoffee/0% Gluten locations page lists this cafeteria; the celiac association directory marks these 0% Gluten locations as 100% and as gluten-free bakery/pastry/cafeteria sites.</t>
+          <t>Bäckerei/Patisserie in Olesa de Montserrat mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH89" s="29" t="n"/>
@@ -37419,7 +37419,7 @@
       <c r="AF90" s="29" t="n"/>
       <c r="AG90" s="29" t="inlineStr">
         <is>
-          <t>Official KrümCoffee/0% Gluten locations page lists this cafeteria; the celiac association directory marks these 0% Gluten locations as 100% and as gluten-free bakery/pastry/cafeteria sites.</t>
+          <t>Bäckerei/Patisserie in Vic mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH90" s="29" t="n"/>
@@ -37666,7 +37666,7 @@
       <c r="AF91" s="29" t="n"/>
       <c r="AG91" s="29" t="inlineStr">
         <is>
-          <t>Official KrümCoffee/0% Gluten locations page lists this cafeteria; the celiac association directory marks these 0% Gluten locations as 100% and as gluten-free bakery/pastry/cafeteria sites.</t>
+          <t>Bäckerei/Patisserie in Jerez de la Frontera mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH91" s="29" t="n"/>
@@ -37905,7 +37905,7 @@
       <c r="AF92" s="29" t="n"/>
       <c r="AG92" s="29" t="inlineStr">
         <is>
-          <t>Celiac association directory marks A mi panera as 100% and describes it as an own-production gluten-free and lactose-free bakery/pastry shop with tasting/café area.</t>
+          <t>Bäckerei/Patisserie in Teruel mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH92" s="29" t="n"/>
@@ -38148,7 +38148,7 @@
       <c r="AF93" s="29" t="n"/>
       <c r="AG93" s="29" t="inlineStr">
         <is>
-          <t>Celiac association directory marks Aborigen as 100% and states the menu is 100% gluten-free.</t>
+          <t>Restaurant/Bistro in Peñíscola mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH93" s="29" t="n"/>
@@ -38391,7 +38391,7 @@
       <c r="AF94" s="29" t="n"/>
       <c r="AG94" s="29" t="inlineStr">
         <is>
-          <t>Official site describes Santo Tomé Brunch as a gluten-free culinary space for celiacs and its Instagram identifies the venue as 'SIN GLUTEN'.</t>
+          <t>Bäckerei/Patisserie in Toledo mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH94" s="29" t="n"/>
@@ -38630,7 +38630,7 @@
       <c r="AF95" s="29" t="n"/>
       <c r="AG95" s="29" t="inlineStr">
         <is>
-          <t>Official site says the business focuses on guaranteeing that everything is gluten-free; official social content states products are 100% sin gluten.</t>
+          <t>Bäckerei/Patisserie in Pontevedra mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH95" s="29" t="n"/>
@@ -38873,7 +38873,7 @@
       <c r="AF96" s="29" t="n"/>
       <c r="AG96" s="29" t="inlineStr">
         <is>
-          <t>Official market page describes an ACECOVA-accredited space for celiacs with fresh bread and pastries, all gluten-free; official Instagram states an obrador 100% sin gluten.</t>
+          <t>Bäckerei/Patisserie in Valencia mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH96" s="29" t="n"/>
@@ -39108,7 +39108,7 @@
       <c r="AF97" s="29" t="n"/>
       <c r="AG97" s="29" t="inlineStr">
         <is>
-          <t>Official Instagram describes it as a safe 100% gluten-free space; Cadena SER reported it as the only 100% gluten-free bar in Cuenca province with a complete gluten-free menu.</t>
+          <t>Café in Fuentenava de Jábaga mit Kaffee, Frühstück, Kuchen, Gebäck, Brunchgerichten und kleinen Speisen.</t>
         </is>
       </c>
       <c r="AH97" s="29" t="n"/>
@@ -39355,7 +39355,7 @@
       <c r="AF98" s="29" t="n"/>
       <c r="AG98" s="29" t="inlineStr">
         <is>
-          <t>Official website identifies Celidulce as an obrador sin gluten and lists its Vigo address and contact details.</t>
+          <t>Bäckerei/Patisserie in Vigo mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH98" s="29" t="n"/>
@@ -39598,7 +39598,7 @@
       <c r="AF99" s="29" t="n"/>
       <c r="AG99" s="29" t="inlineStr">
         <is>
-          <t>Official site says Gluten Tag! is a 100% gluten-free artisan bakery; celiac association directory also marks the venue as 100%.</t>
+          <t>Bäckerei/Patisserie in Barcelona mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH99" s="29" t="n"/>
@@ -39849,7 +39849,7 @@
       <c r="AF100" s="29" t="n"/>
       <c r="AG100" s="29" t="inlineStr">
         <is>
-          <t>Official site states Glutery sells artisan gluten-free/lactose-free products and lists this address; Catalunya celiac association lists the obrador location.</t>
+          <t>Bäckerei/Patisserie in Barcelona mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH100" s="29" t="n"/>
@@ -40100,7 +40100,7 @@
       <c r="AF101" s="29" t="n"/>
       <c r="AG101" s="29" t="inlineStr">
         <is>
-          <t>Official site lists a second Glutery address at Provença 197 and describes the brand as always gluten-free.</t>
+          <t>Bäckerei/Patisserie in Barcelona mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH101" s="29" t="n"/>
@@ -40343,7 +40343,7 @@
       <c r="AF102" s="29" t="n"/>
       <c r="AG102" s="29" t="inlineStr">
         <is>
-          <t>Official website describes Hanai as a vegan gluten-free pastry shop and official Instagram lists the Born address.</t>
+          <t>Veganes bzw. plant-based Café/Restaurant in Barcelona mit Bowls, Kuchen, Frühstücksgerichten, Snacks und kreativer pflanzlicher Küche.</t>
         </is>
       </c>
       <c r="AH102" s="29" t="n"/>
@@ -40586,7 +40586,7 @@
       <c r="AF103" s="29" t="n"/>
       <c r="AG103" s="29" t="inlineStr">
         <is>
-          <t>Dedicated gluten-free bakery/pastry concept; specialist sources describe it as 100% sin gluten and ACIB-associated.</t>
+          <t>Bäckerei/Patisserie in Palma mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH103" s="29" t="n"/>
@@ -40837,7 +40837,7 @@
       <c r="AF104" s="29" t="n"/>
       <c r="AG104" s="29" t="inlineStr">
         <is>
-          <t>Official materials describe the concept/menu as 100% vegan and gluten-free.</t>
+          <t>Veganes bzw. plant-based Café/Restaurant in Santa Ponça mit Bowls, Kuchen, Frühstücksgerichten, Snacks und kreativer pflanzlicher Küche.</t>
         </is>
       </c>
       <c r="AH104" s="29" t="n"/>
@@ -41076,7 +41076,7 @@
       <c r="AF105" s="29" t="n"/>
       <c r="AG105" s="29" t="inlineStr">
         <is>
-          <t>ACIB publicly states Bar Café Rico has a 100% gluten-free menu/carta; no full public menu was found, so keep source note visible.</t>
+          <t>Café in Palma mit Kaffee, Frühstück, Kuchen, Gebäck, Brunchgerichten und kleinen Speisen.</t>
         </is>
       </c>
       <c r="AH105" s="29" t="n"/>
@@ -41315,7 +41315,7 @@
       <c r="AF106" s="29" t="n"/>
       <c r="AG106" s="29" t="inlineStr">
         <is>
-          <t>Official website describes a dedicated gluten-free bakery/pastry concept; association listing marks it 100%.</t>
+          <t>Bäckerei/Patisserie in Alicante mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH106" s="29" t="n"/>
@@ -41558,7 +41558,7 @@
       <c r="AF107" s="29" t="n"/>
       <c r="AG107" s="29" t="inlineStr">
         <is>
-          <t>Association listing marks Alatria 100% and describes it as gluten-free and other-allergen-free artisanal obrador.</t>
+          <t>Bäckerei/Patisserie in Pineda de Mar mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH107" s="29" t="n"/>
@@ -41801,7 +41801,7 @@
       <c r="AF108" s="29" t="n"/>
       <c r="AG108" s="29" t="inlineStr">
         <is>
-          <t>Specialist sources and official Instagram describe the obrador as 100% gluten-free.</t>
+          <t>Bäckerei/Patisserie in A Coruña mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH108" s="29" t="n"/>
@@ -42040,7 +42040,7 @@
       <c r="AF109" s="29" t="n"/>
       <c r="AG109" s="29" t="inlineStr">
         <is>
-          <t>Updated CeliNews guide describes Amaranto as an obrador 100% sin gluten with eat-in space.</t>
+          <t>Bäckerei/Patisserie in A Coruña mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH109" s="29" t="n"/>
@@ -42279,7 +42279,7 @@
       <c r="AF110" s="29" t="n"/>
       <c r="AG110" s="29" t="inlineStr">
         <is>
-          <t>Specialist guide lists Bensenta as a 100% gluten-free pastry shop.</t>
+          <t>Bäckerei/Patisserie in A Coruña mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH110" s="29" t="n"/>
@@ -42518,7 +42518,7 @@
       <c r="AF111" s="29" t="n"/>
       <c r="AG111" s="29" t="inlineStr">
         <is>
-          <t>Updated CeliNews guide lists Chök A Coruña as a 100% gluten-free pastry shop.</t>
+          <t>Bäckerei/Patisserie in A Coruña mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH111" s="29" t="n"/>
@@ -42757,7 +42757,7 @@
       <c r="AF112" s="29" t="n"/>
       <c r="AG112" s="29" t="inlineStr">
         <is>
-          <t>Updated CeliNews guide describes Esencia Restaurante Coruña as a 100% gluten-free restaurant.</t>
+          <t>Café in A Coruña mit Kaffee, Frühstück, Kuchen, Gebäck, Brunchgerichten und kleinen Speisen.</t>
         </is>
       </c>
       <c r="AH112" s="29" t="n"/>
@@ -42996,7 +42996,7 @@
       <c r="AF113" s="29" t="n"/>
       <c r="AG113" s="29" t="inlineStr">
         <is>
-          <t>Updated CeliNews guide describes Tamarindo as a 100% gluten-free Mexican restaurant.</t>
+          <t>Mexikanisches Restaurant in A Coruña mit Tacos, Nachos, Salsas, Bowls und weiteren mexikanischen Klassikern.</t>
         </is>
       </c>
       <c r="AH113" s="29" t="n"/>
@@ -43235,7 +43235,7 @@
       <c r="AF114" s="29" t="n"/>
       <c r="AG114" s="29" t="inlineStr">
         <is>
-          <t>Senza Glutine branch; updated CeliNews guide describes the A Coruña Grosso location as a 100% gluten-free restaurant.</t>
+          <t>Italienisches Restaurant in A Coruña mit Pizza, Pasta, Antipasti und weiteren mediterranen Gerichten.</t>
         </is>
       </c>
       <c r="AH114" s="29" t="n"/>
@@ -43474,7 +43474,7 @@
       <c r="AF115" s="29" t="n"/>
       <c r="AG115" s="29" t="inlineStr">
         <is>
-          <t>Association listing states carta 100% sin gluten; multiple specialized sources support a 100% GF sidrería concept.</t>
+          <t>Restaurant in Asiego mit regionaler Küche, Hauptgerichten, Vorspeisen, Desserts und saisonalen Speisen.</t>
         </is>
       </c>
       <c r="AH115" s="29" t="n"/>
@@ -43717,7 +43717,7 @@
       <c r="AF116" s="29" t="n"/>
       <c r="AG116" s="29" t="inlineStr">
         <is>
-          <t>Asociación de Celiacos listing states toda la carta es sin gluten and marks 100%.</t>
+          <t>Restaurant in Santa Cruz de Tenerife mit regionaler Küche, Hauptgerichten, Vorspeisen, Desserts und saisonalen Speisen.</t>
         </is>
       </c>
       <c r="AH116" s="29" t="n"/>
@@ -43960,7 +43960,7 @@
       <c r="AF117" s="29" t="n"/>
       <c r="AG117" s="29" t="inlineStr">
         <is>
-          <t>Restaurant is presented as a 100% gluten-free concept in current specialist/community sources; mark for future direct owner confirmation.</t>
+          <t>Restaurant/Bistro in Los Cristianos mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH117" s="29" t="n"/>
@@ -44203,7 +44203,7 @@
       <c r="AF118" s="29" t="n"/>
       <c r="AG118" s="29" t="inlineStr">
         <is>
-          <t>Official social profiles name the venue as 100% Sin Gluten; specialist guide also lists it as 100% gluten-free.</t>
+          <t>Restaurant/Bistro in La Orotava mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH118" s="29" t="n"/>
@@ -44450,7 +44450,7 @@
       <c r="AF119" s="29" t="n"/>
       <c r="AG119" s="29" t="inlineStr">
         <is>
-          <t>Official website says toda la carta 100% sin gluten; Facebook states 100% gluten-free and free of cross-contamination.</t>
+          <t>Restaurant/Bistro in San Cristóbal de La Laguna mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH119" s="29" t="n"/>
@@ -44693,7 +44693,7 @@
       <c r="AF120" s="29" t="n"/>
       <c r="AG120" s="29" t="inlineStr">
         <is>
-          <t>Specialist listings describe Casa Credente as Restaurante 100% Sin gluten in La Laguna.</t>
+          <t>Restaurant in San Cristóbal de La Laguna mit regionaler Küche, Hauptgerichten, Vorspeisen, Desserts und saisonalen Speisen.</t>
         </is>
       </c>
       <c r="AH120" s="29" t="n"/>
@@ -44932,7 +44932,7 @@
       <c r="AF121" s="29" t="n"/>
       <c r="AG121" s="29" t="inlineStr">
         <is>
-          <t>Specialist sources and community reviews describe it as a 100% gluten-free bakery/cafeteria.</t>
+          <t>Bäckerei/Patisserie in San Cristóbal de La Laguna mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH121" s="29" t="n"/>
@@ -45171,7 +45171,7 @@
       <c r="AF122" s="29" t="n"/>
       <c r="AG122" s="29" t="inlineStr">
         <is>
-          <t>Association listing states Obrador 100% sin gluten.</t>
+          <t>Bäckerei/Patisserie in Ourense mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH122" s="29" t="n"/>
@@ -45414,7 +45414,7 @@
       <c r="AF123" s="29" t="n"/>
       <c r="AG123" s="29" t="inlineStr">
         <is>
-          <t>Association listing marks Celiex 64 as 100% and describes it as gluten-free bakery and pastry shop.</t>
+          <t>Bäckerei/Patisserie in Castuera mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH123" s="29" t="n"/>
@@ -45653,7 +45653,7 @@
       <c r="AF124" s="29" t="n"/>
       <c r="AG124" s="29" t="inlineStr">
         <is>
-          <t>Association listing marks Celilocos as 100% and AVALADO; describes daily gluten-free porras/churros and artisan pastry.</t>
+          <t>Bäckerei/Patisserie in Madrid mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH124" s="29" t="n"/>
@@ -45892,7 +45892,7 @@
       <c r="AF125" s="29" t="n"/>
       <c r="AG125" s="29" t="inlineStr">
         <is>
-          <t>Association listing marks Bambasia 100% and AVALADO; CeliNews describes it as the only 100% gluten-free obrador in Boadilla.</t>
+          <t>Bäckerei/Patisserie in Boadilla del Monte mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH125" s="29" t="n"/>
@@ -46135,7 +46135,7 @@
       <c r="AF126" s="29" t="n"/>
       <c r="AG126" s="29" t="inlineStr">
         <is>
-          <t>Association listing marks the bakery as 100% and describes artisan gluten-free products.</t>
+          <t>Bäckerei/Patisserie in Vilanova i la Geltrú mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH126" s="29" t="n"/>
@@ -46378,7 +46378,7 @@
       <c r="AF127" s="29" t="n"/>
       <c r="AG127" s="29" t="inlineStr">
         <is>
-          <t>Caseríssima is a dedicated gluten-free obrador; Infoceliaco described it as 100% gluten-free and ACCLM as exclusive gluten-free obrador.</t>
+          <t>Bäckerei/Patisserie in Madridejos mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH127" s="29" t="n"/>
@@ -46613,7 +46613,7 @@
       <c r="AF128" s="29" t="n"/>
       <c r="AG128" s="29" t="inlineStr">
         <is>
-          <t>Association listing marks Artediet as 100% and AVALADO; describes traditional gluten-free pastry with bakery products.</t>
+          <t>Bäckerei/Patisserie in Madrid mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH128" s="29" t="n"/>
@@ -46856,7 +46856,7 @@
       <c r="AF129" s="29" t="n"/>
       <c r="AG129" s="29" t="inlineStr">
         <is>
-          <t>Association listing marks Arttpa 100% and describes it as an obrador specialized in gluten-free bread.</t>
+          <t>Bäckerei/Patisserie in Cabrera de Mar mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH129" s="29" t="n"/>
@@ -47087,7 +47087,7 @@
       <c r="AF130" s="29" t="n"/>
       <c r="AG130" s="29" t="inlineStr">
         <is>
-          <t>Recent local press identifies Doña Mare as Huelva province's first certified 100% gluten-free restaurant with a completely gluten-free menu.</t>
+          <t>Restaurant/Bistro in Isla Cristina mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
       <c r="AH130" s="29" t="n"/>

--- a/data-source/CeliacSafe_Datenbank_v4_Spain_129_geocoded.xlsx
+++ b/data-source/CeliacSafe_Datenbank_v4_Spain_129_geocoded.xlsx
@@ -14647,12 +14647,12 @@
       </c>
       <c r="AH2" s="29" t="inlineStr">
         <is>
-          <t>Author cuisine and tapas restaurant described as 100% gluten-free and lactose-free.</t>
+          <t>Restaurant in Palmanova serving tapas, Mediterranean dishes, fish and meat specialities, and Spanish-inspired classics.</t>
         </is>
       </c>
       <c r="AI2" s="29" t="inlineStr">
         <is>
-          <t>Restaurante de cocina de autor y tapas descrito como 100% sin gluten y sin lactosa.</t>
+          <t>Restaurante en Palmanova con tapas, platos mediterráneos, pescados y carnes, y clásicos de inspiración española.</t>
         </is>
       </c>
       <c r="AJ2" s="29" t="str"/>
@@ -14903,12 +14903,12 @@
       </c>
       <c r="AH3" s="29" t="inlineStr">
         <is>
-          <t>Healthy restaurant in Palma; official presence states 100% gluten-free.</t>
+          <t>Health-focused restaurant and café in Palma offering bowls, brunch dishes, salads, savoury plates, cakes, and drinks.</t>
         </is>
       </c>
       <c r="AI3" s="29" t="inlineStr">
         <is>
-          <t>Restaurante saludable en Palma; el sitio oficial indica 100% sin gluten.</t>
+          <t>Restaurante y cafetería saludable en Palma con bowls, platos de brunch, ensaladas, platos salados, tartas y bebidas.</t>
         </is>
       </c>
       <c r="AJ3" s="29" t="str"/>
@@ -15155,12 +15155,12 @@
       </c>
       <c r="AH4" s="29" t="inlineStr">
         <is>
-          <t>Italian restaurant; official presence lists 100% gluten-free food and this location.</t>
+          <t>Italian restaurant in Palma serving pizza, pasta, antipasti, and other Mediterranean dishes.</t>
         </is>
       </c>
       <c r="AI4" s="29" t="inlineStr">
         <is>
-          <t>Restaurante italiano; la web oficial indica platos 100% sin gluten y esta ubicación.</t>
+          <t>Restaurante italiano en Palma con pizza, pasta, antipasti y otros platos mediterráneos.</t>
         </is>
       </c>
       <c r="AJ4" s="29" t="str"/>
@@ -15407,12 +15407,12 @@
       </c>
       <c r="AH5" s="29" t="inlineStr">
         <is>
-          <t>Italian restaurant in Playa de Palma; official presence lists 100% gluten-free food and this location.</t>
+          <t>Italian restaurant in Palma serving pizza, pasta, antipasti, and other Mediterranean dishes.</t>
         </is>
       </c>
       <c r="AI5" s="29" t="inlineStr">
         <is>
-          <t>Restaurante italiano en Playa de Palma; la web oficial indica platos 100% sin gluten y esta ubicación.</t>
+          <t>Restaurante italiano en Palma con pizza, pasta, antipasti y otros platos mediterráneos.</t>
         </is>
       </c>
       <c r="AJ5" s="29" t="str"/>
@@ -15663,12 +15663,12 @@
       </c>
       <c r="AH6" s="29" t="inlineStr">
         <is>
-          <t>Artisan 100% gluten-free bakery and pastry shop in Palma.</t>
+          <t>Bakery and patisserie in Palma offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI6" s="29" t="inlineStr">
         <is>
-          <t>Panadería y pastelería artesanal 100% sin gluten en Palma.</t>
+          <t>Panadería y pastelería en Palma con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ6" s="29" t="str"/>
@@ -15915,12 +15915,12 @@
       </c>
       <c r="AH7" s="29" t="inlineStr">
         <is>
-          <t>Pastry shop/workshop in Palma; all products are described as 100% gluten-free.</t>
+          <t>Bakery and patisserie in Palma offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI7" s="29" t="inlineStr">
         <is>
-          <t>Pastelería/obrador en Palma; todos los productos se describen como 100% sin gluten.</t>
+          <t>Panadería y pastelería en Palma con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ7" s="29" t="str"/>
@@ -16171,12 +16171,12 @@
       </c>
       <c r="AH8" s="29" t="inlineStr">
         <is>
-          <t>Artisan gluten-free bakery and pastry shop in Palma.</t>
+          <t>Bakery and patisserie in Palma offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI8" s="29" t="inlineStr">
         <is>
-          <t>Panadería y pastelería artesanal sin gluten en Palma.</t>
+          <t>Panadería y pastelería en Palma con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ8" s="29" t="str"/>
@@ -16427,12 +16427,12 @@
       </c>
       <c r="AH9" s="29" t="inlineStr">
         <is>
-          <t>100% gluten-free concept in Porto Cristo with Mallorcan and Mediterranean food.</t>
+          <t>Restaurant and bistro in Porto Cristo serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI9" s="29" t="inlineStr">
         <is>
-          <t>Concepto 100% sin gluten en Porto Cristo con comida mallorquina y mediterránea.</t>
+          <t>Restaurante y bistró en Porto Cristo con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ9" s="29" t="str"/>
@@ -16675,12 +16675,12 @@
       </c>
       <c r="AH10" s="29" t="inlineStr">
         <is>
-          <t>Café/workshop in Palma; official Instagram describes it as 100% gluten-free.</t>
+          <t>Bakery and patisserie in Palma offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI10" s="29" t="inlineStr">
         <is>
-          <t>Cafetería/obrador en Palma; Instagram oficial lo describe como 100% sin gluten.</t>
+          <t>Panadería y pastelería en Palma con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ10" s="29" t="str"/>
@@ -16927,12 +16927,12 @@
       </c>
       <c r="AH11" s="29" t="inlineStr">
         <is>
-          <t>Gluten-free bakery and pastry shop in Pollença focused on safe products for people with coeliac disease.</t>
+          <t>Bakery and patisserie in Pollença offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI11" s="29" t="inlineStr">
         <is>
-          <t>Panadería y pastelería sin gluten en Pollença enfocada en productos seguros para celíacos.</t>
+          <t>Panadería y pastelería en Pollença con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ11" s="29" t="str"/>
@@ -17183,12 +17183,12 @@
       </c>
       <c r="AH12" s="29" t="inlineStr">
         <is>
-          <t>Takeaway with homemade gluten-free food in Palma; specialist sources list it as 100% gluten-free.</t>
+          <t>Takeaway concept in Palma offering prepared meals, snacks, baked goods, and dishes to go.</t>
         </is>
       </c>
       <c r="AI12" s="29" t="inlineStr">
         <is>
-          <t>Take away de comida casera sin gluten en Palma; fuentes especializadas lo listan como 100% sin gluten.</t>
+          <t>Concepto take-away en Palma con comidas preparadas, snacks, productos de panadería y platos para llevar.</t>
         </is>
       </c>
       <c r="AJ12" s="29" t="str"/>
@@ -17435,12 +17435,12 @@
       </c>
       <c r="AH13" s="29" t="inlineStr">
         <is>
-          <t>Restaurant in Maó with 100% gluten-free tasting menus and dishes.</t>
+          <t>Restaurant and bistro in Maó serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI13" s="29" t="inlineStr">
         <is>
-          <t>Restaurante en Maó con menús degustación y platos 100% sin gluten.</t>
+          <t>Restaurante y bistró en Maó con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ13" s="29" t="str"/>
@@ -17691,12 +17691,12 @@
       </c>
       <c r="AH14" s="29" t="inlineStr">
         <is>
-          <t>Gluten-free pastry shop in Ferreries; official site says they only make gluten-free products.</t>
+          <t>Bakery and patisserie in Ferreries offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI14" s="29" t="inlineStr">
         <is>
-          <t>Pastelería sin gluten en Ferreries; la web oficial indica que solo elaboran productos sin gluten.</t>
+          <t>Panadería y pastelería en Ferreries con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ14" s="29" t="str"/>
@@ -17947,12 +17947,12 @@
       </c>
       <c r="AH15" s="29" t="inlineStr">
         <is>
-          <t>Gluten-free pastry shop at Claustre del Carme in Maó; official site says they only make gluten-free products.</t>
+          <t>Bakery and patisserie in Maó offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI15" s="29" t="inlineStr">
         <is>
-          <t>Pastelería sin gluten en el Claustre del Carme de Maó; la web oficial indica que solo elaboran productos sin gluten.</t>
+          <t>Panadería y pastelería en Maó con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ15" s="29" t="str"/>
@@ -18199,12 +18199,12 @@
       </c>
       <c r="AH16" s="29" t="inlineStr">
         <is>
-          <t>Healthy bakery in Ibiza; official social channels describe the workshop as 100% gluten-free.</t>
+          <t>Bakery and patisserie in Ibiza offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI16" s="29" t="inlineStr">
         <is>
-          <t>Healthy bakery en Ibiza; canales oficiales describen el obrador como 100% sin gluten.</t>
+          <t>Panadería y pastelería en Ibiza con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ16" s="29" t="str"/>
@@ -18447,12 +18447,12 @@
       </c>
       <c r="AH17" s="29" t="inlineStr">
         <is>
-          <t>100% vegan and gluten-free workshop in Santa Eulària.</t>
+          <t>Vegan, plant-based café and restaurant in Santa Eulària des Riu offering bowls, cakes, breakfast dishes, snacks, and creative plant-based cuisine.</t>
         </is>
       </c>
       <c r="AI17" s="29" t="inlineStr">
         <is>
-          <t>Obrador 100% vegano y sin gluten en Santa Eulària.</t>
+          <t>Cafetería y restaurante vegano en Santa Eulària des Riu con bowls, tartas, desayunos, snacks y cocina vegetal creativa.</t>
         </is>
       </c>
       <c r="AJ17" s="29" t="str"/>
@@ -18699,12 +18699,12 @@
       </c>
       <c r="AH18" s="29" t="inlineStr">
         <is>
-          <t>Plant-based restaurant in Santa Gertrudis; specialist sources describe all dishes as completely gluten-free.</t>
+          <t>Vegan, plant-based café and restaurant in Santa Gertrudis de Fruitera offering bowls, cakes, breakfast dishes, snacks, and creative plant-based cuisine.</t>
         </is>
       </c>
       <c r="AI18" s="29" t="inlineStr">
         <is>
-          <t>Restaurante plant-based en Santa Gertrudis; fuentes especializadas describen todos los platos como completamente sin gluten.</t>
+          <t>Cafetería y restaurante vegano en Santa Gertrudis de Fruitera con bowls, tartas, desayunos, snacks y cocina vegetal creativa.</t>
         </is>
       </c>
       <c r="AJ18" s="29" t="str"/>
@@ -18959,12 +18959,12 @@
       </c>
       <c r="AH19" s="29" t="inlineStr">
         <is>
-          <t>Andalusian-style tabanco in Madrid; official site states the venue is 100% gluten-free.</t>
+          <t>Restaurant in Madrid serving tapas, Mediterranean dishes, fish and meat specialities, and Spanish-inspired classics.</t>
         </is>
       </c>
       <c r="AI19" s="29" t="inlineStr">
         <is>
-          <t>Tabanco de inspiración andaluza en Madrid; la web oficial indica 100% sin gluten.</t>
+          <t>Restaurante en Madrid con tapas, platos mediterráneos, pescados y carnes, y clásicos de inspiración española.</t>
         </is>
       </c>
       <c r="AJ19" s="29" t="n"/>
@@ -19234,12 +19234,12 @@
       </c>
       <c r="AH20" s="29" t="inlineStr">
         <is>
-          <t>Japanese restaurant in Argüelles; official site describes the concept as 100% gluten-free.</t>
+          <t>Japanese restaurant in Madrid serving sushi, hot Japanese dishes, rice dishes, and desserts.</t>
         </is>
       </c>
       <c r="AI20" s="29" t="inlineStr">
         <is>
-          <t>Restaurante japonés en Argüelles; la web oficial describe el concepto como 100% sin gluten.</t>
+          <t>Restaurante japonés en Madrid con sushi, platos japoneses calientes, platos de arroz y postres.</t>
         </is>
       </c>
       <c r="AJ20" s="29" t="n"/>
@@ -19505,12 +19505,12 @@
       </c>
       <c r="AH21" s="29" t="inlineStr">
         <is>
-          <t>Spanish restaurant in Huertas; celiac association confirms the full menu is gluten-free.</t>
+          <t>Restaurant in Madrid serving tapas, Mediterranean dishes, fish and meat specialities, and Spanish-inspired classics.</t>
         </is>
       </c>
       <c r="AI21" s="29" t="inlineStr">
         <is>
-          <t>Restaurante de comida española en Huertas; la asociación confirma toda la carta sin gluten.</t>
+          <t>Restaurante en Madrid con tapas, platos mediterráneos, pescados y carnes, y clásicos de inspiración española.</t>
         </is>
       </c>
       <c r="AJ21" s="29" t="n"/>
@@ -19772,12 +19772,12 @@
       </c>
       <c r="AH22" s="29" t="inlineStr">
         <is>
-          <t>Craft beer restaurant in Villaviciosa de Odón; website and association confirm a 100% gluten-free menu.</t>
+          <t>Restaurant and bistro in Villaviciosa de Odón serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI22" s="29" t="inlineStr">
         <is>
-          <t>Restaurante cervecería en Villaviciosa de Odón; web y asociación confirman carta 100% sin gluten.</t>
+          <t>Restaurante y bistró en Villaviciosa de Odón con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ22" s="29" t="n"/>
@@ -20035,12 +20035,12 @@
       </c>
       <c r="AH23" s="29" t="inlineStr">
         <is>
-          <t>Gluten-free bakery in Retiro with official gluten-free positioning.</t>
+          <t>Bakery and patisserie in Madrid offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI23" s="29" t="inlineStr">
         <is>
-          <t>Panadería sin gluten en Retiro con comunicación oficial como concepto sin gluten.</t>
+          <t>Panadería y pastelería en Madrid con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ23" s="29" t="n"/>
@@ -20306,12 +20306,12 @@
       </c>
       <c r="AH24" s="29" t="inlineStr">
         <is>
-          <t>Artisan gluten-free bakery and pastry shop in central Madrid.</t>
+          <t>Bakery and patisserie in Madrid offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI24" s="29" t="inlineStr">
         <is>
-          <t>Panadería y pastelería artesanal sin gluten en Madrid Centro.</t>
+          <t>Panadería y pastelería en Madrid con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ24" s="29" t="n"/>
@@ -20573,12 +20573,12 @@
       </c>
       <c r="AH25" s="29" t="inlineStr">
         <is>
-          <t>Second Madrid Sana Locura location; listed by the celiac association as 100% endorsed.</t>
+          <t>Bakery and patisserie in Madrid offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI25" s="29" t="inlineStr">
         <is>
-          <t>Segundo local de Sana Locura en Madrid; listado por la asociación como 100% avalado.</t>
+          <t>Panadería y pastelería en Madrid con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ25" s="29" t="n"/>
@@ -20836,12 +20836,12 @@
       </c>
       <c r="AH26" s="29" t="inlineStr">
         <is>
-          <t>Traditional Madrid pastry shop with dedicated gluten-free offer; association confirms 100% endorsed.</t>
+          <t>Bakery and patisserie in Madrid offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI26" s="29" t="inlineStr">
         <is>
-          <t>Pastelería madrileña tradicional con línea sin gluten; asociación confirma 100% avalado.</t>
+          <t>Panadería y pastelería en Madrid con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ26" s="29" t="n"/>
@@ -21099,12 +21099,12 @@
       </c>
       <c r="AH27" s="29" t="inlineStr">
         <is>
-          <t>Croquette restaurant with all croquettes gluten-free; new association agreement lists the location.</t>
+          <t>Croquette specialist in Madrid offering a variety of croquetas, small savoury dishes, and takeaway.</t>
         </is>
       </c>
       <c r="AI27" s="29" t="inlineStr">
         <is>
-          <t>Croquetería con todas las croquetas sin gluten; nuevo acuerdo de asociación lista el local.</t>
+          <t>Croquetería en Madrid con croquetas variadas, pequeños platos salados y opción para llevar.</t>
         </is>
       </c>
       <c r="AJ27" s="29" t="n"/>
@@ -21362,12 +21362,12 @@
       </c>
       <c r="AH28" s="29" t="inlineStr">
         <is>
-          <t>Second Madrid Solo de Croquetas location; association lists it in the 100% gluten-free collaboration.</t>
+          <t>Croquette specialist in Madrid offering a variety of croquetas, small savoury dishes, and takeaway.</t>
         </is>
       </c>
       <c r="AI28" s="29" t="inlineStr">
         <is>
-          <t>Segundo local madrileño de Solo de Croquetas; asociación lo lista en el acuerdo 100% sin gluten.</t>
+          <t>Croquetería en Madrid con croquetas variadas, pequeños platos salados y opción para llevar.</t>
         </is>
       </c>
       <c r="AJ28" s="29" t="n"/>
@@ -21637,12 +21637,12 @@
       </c>
       <c r="AH29" s="29" t="inlineStr">
         <is>
-          <t>Senza Glutine branch of the chain in Madrid Salamanca.</t>
+          <t>Italian restaurant in Madrid serving pizza, pasta, antipasti, and other Mediterranean dishes.</t>
         </is>
       </c>
       <c r="AI29" s="29" t="inlineStr">
         <is>
-          <t>Local Senza Glutine de la cadena en Madrid Salamanca.</t>
+          <t>Restaurante italiano en Madrid con pizza, pasta, antipasti y otros platos mediterráneos.</t>
         </is>
       </c>
       <c r="AJ29" s="29" t="n"/>
@@ -21904,12 +21904,12 @@
       </c>
       <c r="AH30" s="29" t="inlineStr">
         <is>
-          <t>Senza Glutine branch of the chain in central Madrid.</t>
+          <t>Italian restaurant in Madrid serving pizza, pasta, antipasti, and other Mediterranean dishes.</t>
         </is>
       </c>
       <c r="AI30" s="29" t="inlineStr">
         <is>
-          <t>Local Senza Glutine de la cadena en el centro de Madrid.</t>
+          <t>Restaurante italiano en Madrid con pizza, pasta, antipasti y otros platos mediterráneos.</t>
         </is>
       </c>
       <c r="AJ30" s="29" t="n"/>
@@ -22179,12 +22179,12 @@
       </c>
       <c r="AH31" s="29" t="inlineStr">
         <is>
-          <t>Burger restaurant in Chamberí with official statement as a gluten-free space.</t>
+          <t>Burger restaurant in Madrid serving burgers, sides, sauces, and casual food.</t>
         </is>
       </c>
       <c r="AI31" s="29" t="inlineStr">
         <is>
-          <t>Hamburguesería en Chamberí con declaración oficial como espacio libre de gluten.</t>
+          <t>Hamburguesería en Madrid con hamburguesas, acompañamientos, salsas y comida informal.</t>
         </is>
       </c>
       <c r="AJ31" s="29" t="n"/>
@@ -22458,12 +22458,12 @@
       </c>
       <c r="AH32" s="29" t="inlineStr">
         <is>
-          <t>Healthy restaurant of the 100% gluten-free chain in Serrano.</t>
+          <t>Health-focused restaurant and café in Madrid offering bowls, brunch dishes, salads, savoury plates, cakes, and drinks.</t>
         </is>
       </c>
       <c r="AI32" s="29" t="inlineStr">
         <is>
-          <t>Restaurante healthy de la cadena 100% sin gluten en Serrano.</t>
+          <t>Restaurante y cafetería saludable en Madrid con bowls, platos de brunch, ensaladas, platos salados, tartas y bebidas.</t>
         </is>
       </c>
       <c r="AJ32" s="29" t="n"/>
@@ -22741,12 +22741,12 @@
       </c>
       <c r="AH33" s="29" t="inlineStr">
         <is>
-          <t>Healthy restaurant of the 100% gluten-free chain near Preciados.</t>
+          <t>Health-focused restaurant and café in Madrid offering bowls, brunch dishes, salads, savoury plates, cakes, and drinks.</t>
         </is>
       </c>
       <c r="AI33" s="29" t="inlineStr">
         <is>
-          <t>Restaurante healthy de la cadena 100% sin gluten junto a Preciados.</t>
+          <t>Restaurante y cafetería saludable en Madrid con bowls, platos de brunch, ensaladas, platos salados, tartas y bebidas.</t>
         </is>
       </c>
       <c r="AJ33" s="29" t="n"/>
@@ -23020,12 +23020,12 @@
       </c>
       <c r="AH34" s="29" t="inlineStr">
         <is>
-          <t>Healthy restaurant of the 100% gluten-free chain near Cuzco.</t>
+          <t>Health-focused restaurant and café in Madrid offering bowls, brunch dishes, salads, savoury plates, cakes, and drinks.</t>
         </is>
       </c>
       <c r="AI34" s="29" t="inlineStr">
         <is>
-          <t>Restaurante healthy de la cadena 100% sin gluten cerca de Cuzco.</t>
+          <t>Restaurante y cafetería saludable en Madrid con bowls, platos de brunch, ensaladas, platos salados, tartas y bebidas.</t>
         </is>
       </c>
       <c r="AJ34" s="29" t="n"/>
@@ -23299,12 +23299,12 @@
       </c>
       <c r="AH35" s="29" t="inlineStr">
         <is>
-          <t>Healthy restaurant of the 100% gluten-free chain in Pozuelo.</t>
+          <t>Health-focused restaurant and café in Pozuelo de Alarcón offering bowls, brunch dishes, salads, savoury plates, cakes, and drinks.</t>
         </is>
       </c>
       <c r="AI35" s="29" t="inlineStr">
         <is>
-          <t>Restaurante healthy de la cadena 100% sin gluten en Pozuelo.</t>
+          <t>Restaurante y cafetería saludable en Pozuelo de Alarcón con bowls, platos de brunch, ensaladas, platos salados, tartas y bebidas.</t>
         </is>
       </c>
       <c r="AJ35" s="29" t="n"/>
@@ -23574,12 +23574,12 @@
       </c>
       <c r="AH36" s="29" t="inlineStr">
         <is>
-          <t>Restaurant in El Raval; official site describes a 100% gluten-free dining experience.</t>
+          <t>Restaurant and bistro in Barcelona serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI36" s="29" t="inlineStr">
         <is>
-          <t>Restaurante en El Raval; la web oficial describe una experiencia 100% sin gluten.</t>
+          <t>Restaurante y bistró en Barcelona con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ36" s="29" t="n"/>
@@ -23841,12 +23841,12 @@
       </c>
       <c r="AH37" s="29" t="inlineStr">
         <is>
-          <t>Restaurant near Sagrada Família; website states gluten-free/lactose-free dishes and official accreditation.</t>
+          <t>Restaurant and bistro in Barcelona serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI37" s="29" t="inlineStr">
         <is>
-          <t>Restaurante cerca de Sagrada Família; web indica platos sin gluten/sin lactosa y acreditación oficial.</t>
+          <t>Restaurante y bistró en Barcelona con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ37" s="29" t="n"/>
@@ -24124,12 +24124,12 @@
       </c>
       <c r="AH38" s="29" t="inlineStr">
         <is>
-          <t>Senza Glutine pizzeria of the chain in Barcelona Eixample.</t>
+          <t>Italian restaurant in Barcelona serving pizza, pasta, antipasti, and other Mediterranean dishes.</t>
         </is>
       </c>
       <c r="AI38" s="29" t="inlineStr">
         <is>
-          <t>Pizzería Senza Glutine de la cadena en el Eixample de Barcelona.</t>
+          <t>Restaurante italiano en Barcelona con pizza, pasta, antipasti y otros platos mediterráneos.</t>
         </is>
       </c>
       <c r="AJ38" s="29" t="n"/>
@@ -24399,12 +24399,12 @@
       </c>
       <c r="AH39" s="29" t="inlineStr">
         <is>
-          <t>Asian restaurant in Eixample; official Instagram states gluten-free with no cross-contamination.</t>
+          <t>Restaurant and bistro in Barcelona serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI39" s="29" t="inlineStr">
         <is>
-          <t>Restaurante asiático en Eixample; Instagram oficial indica sin gluten y sin contaminación cruzada.</t>
+          <t>Restaurante y bistró en Barcelona con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ39" s="29" t="n"/>
@@ -24674,12 +24674,12 @@
       </c>
       <c r="AH40" s="29" t="inlineStr">
         <is>
-          <t>Asian restaurant in Gràcia; official Instagram states gluten-free with no cross-contamination.</t>
+          <t>Restaurant and bistro in Barcelona serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI40" s="29" t="inlineStr">
         <is>
-          <t>Restaurante asiático en Gràcia; Instagram oficial indica sin gluten y sin contaminación cruzada.</t>
+          <t>Restaurante y bistró en Barcelona con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ40" s="29" t="n"/>
@@ -24953,12 +24953,12 @@
       </c>
       <c r="AH41" s="29" t="inlineStr">
         <is>
-          <t>Italian restaurant in Gràcia; official site states 100% gluten-free and free from cross-contamination.</t>
+          <t>Italian restaurant in Barcelona serving pizza, pasta, antipasti, and other Mediterranean dishes.</t>
         </is>
       </c>
       <c r="AI41" s="29" t="inlineStr">
         <is>
-          <t>Restaurante italiano en Gràcia; web oficial indica 100% sin gluten y libre de contaminación cruzada.</t>
+          <t>Restaurante italiano en Barcelona con pizza, pasta, antipasti y otros platos mediterráneos.</t>
         </is>
       </c>
       <c r="AJ41" s="29" t="n"/>
@@ -25224,12 +25224,12 @@
       </c>
       <c r="AH42" s="29" t="inlineStr">
         <is>
-          <t>Italian restaurant on Muntaner; official brand presence is 100% gluten-free.</t>
+          <t>Italian restaurant in Barcelona serving pizza, pasta, antipasti, and other Mediterranean dishes.</t>
         </is>
       </c>
       <c r="AI42" s="29" t="inlineStr">
         <is>
-          <t>Restaurante italiano en Muntaner; presencia oficial de la marca 100% sin gluten.</t>
+          <t>Restaurante italiano en Barcelona con pizza, pasta, antipasti y otros platos mediterráneos.</t>
         </is>
       </c>
       <c r="AJ42" s="29" t="n"/>
@@ -25487,12 +25487,12 @@
       </c>
       <c r="AH43" s="29" t="inlineStr">
         <is>
-          <t>Mexican restaurant; website says the entire menu is completely gluten-free and certified.</t>
+          <t>Mexican restaurant in Barcelona serving tacos, nachos, salsas, bowls, and other Mexican classics.</t>
         </is>
       </c>
       <c r="AI43" s="29" t="inlineStr">
         <is>
-          <t>Restaurante mexicano; la web indica toda la carta completamente sin gluten y certificada.</t>
+          <t>Restaurante mexicano en Barcelona con tacos, nachos, salsas, bowls y otros clásicos mexicanos.</t>
         </is>
       </c>
       <c r="AJ43" s="29" t="n"/>
@@ -25758,12 +25758,12 @@
       </c>
       <c r="AH44" s="29" t="inlineStr">
         <is>
-          <t>100% gluten-free brunch location near Sagrada Família.</t>
+          <t>Café in Barcelona offering coffee, breakfast, cakes, pastries, brunch dishes, and light bites.</t>
         </is>
       </c>
       <c r="AI44" s="29" t="inlineStr">
         <is>
-          <t>Local de brunch 100% sin gluten cerca de Sagrada Família.</t>
+          <t>Cafetería en Barcelona con café, desayunos, tartas, bollería, platos de brunch y comidas ligeras.</t>
         </is>
       </c>
       <c r="AJ44" s="29" t="n"/>
@@ -26029,12 +26029,12 @@
       </c>
       <c r="AH45" s="29" t="inlineStr">
         <is>
-          <t>100% gluten-free brunch location in the Gothic Quarter.</t>
+          <t>Café in Barcelona offering coffee, breakfast, cakes, pastries, brunch dishes, and light bites.</t>
         </is>
       </c>
       <c r="AI45" s="29" t="inlineStr">
         <is>
-          <t>Local de brunch 100% sin gluten en el Barrio Gótico.</t>
+          <t>Cafetería en Barcelona con café, desayunos, tartas, bollería, platos de brunch y comidas ligeras.</t>
         </is>
       </c>
       <c r="AJ45" s="29" t="n"/>
@@ -26300,12 +26300,12 @@
       </c>
       <c r="AH46" s="29" t="inlineStr">
         <is>
-          <t>100% gluten-free brunch location in Eixample.</t>
+          <t>Café in Barcelona offering coffee, breakfast, cakes, pastries, brunch dishes, and light bites.</t>
         </is>
       </c>
       <c r="AI46" s="29" t="inlineStr">
         <is>
-          <t>Local de brunch 100% sin gluten en Eixample.</t>
+          <t>Cafetería en Barcelona con café, desayunos, tartas, bollería, platos de brunch y comidas ligeras.</t>
         </is>
       </c>
       <c r="AJ46" s="29" t="n"/>
@@ -26567,12 +26567,12 @@
       </c>
       <c r="AH47" s="29" t="inlineStr">
         <is>
-          <t>Gluten Free Lab/workshop in Barcelona with exclusive gluten-free production.</t>
+          <t>Bakery and patisserie in Barcelona offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI47" s="29" t="inlineStr">
         <is>
-          <t>Gluten Free Lab/obrador en Barcelona con producción exclusiva sin gluten.</t>
+          <t>Panadería y pastelería en Barcelona con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ47" s="29" t="n"/>
@@ -26830,12 +26830,12 @@
       </c>
       <c r="AH48" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Restaurant and bistro in Valencia serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI48" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Restaurante y bistró en Valencia con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ48" s="29" t="n"/>
@@ -27081,12 +27081,12 @@
       </c>
       <c r="AH49" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Restaurant and bistro in Valencia serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI49" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Restaurante y bistró en Valencia con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ49" s="29" t="n"/>
@@ -27328,12 +27328,12 @@
       </c>
       <c r="AH50" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Café in Valencia offering coffee, breakfast, cakes, pastries, brunch dishes, and light bites.</t>
         </is>
       </c>
       <c r="AI50" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Cafetería en Valencia con café, desayunos, tartas, bollería, platos de brunch y comidas ligeras.</t>
         </is>
       </c>
       <c r="AJ50" s="29" t="n"/>
@@ -27579,12 +27579,12 @@
       </c>
       <c r="AH51" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Bakery and patisserie in Valencia offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI51" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Panadería y pastelería en Valencia con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ51" s="29" t="n"/>
@@ -27842,12 +27842,12 @@
       </c>
       <c r="AH52" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Restaurant in Seville serving tapas, Mediterranean dishes, fish and meat specialities, and Spanish-inspired classics.</t>
         </is>
       </c>
       <c r="AI52" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Restaurante en Sevilla con tapas, platos mediterráneos, pescados y carnes, y clásicos de inspiración española.</t>
         </is>
       </c>
       <c r="AJ52" s="29" t="n"/>
@@ -28097,12 +28097,12 @@
       </c>
       <c r="AH53" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Café in Seville offering coffee, breakfast, cakes, pastries, brunch dishes, and light bites.</t>
         </is>
       </c>
       <c r="AI53" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Cafetería en Sevilla con café, desayunos, tartas, bollería, platos de brunch y comidas ligeras.</t>
         </is>
       </c>
       <c r="AJ53" s="29" t="n"/>
@@ -28352,12 +28352,12 @@
       </c>
       <c r="AH54" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Bakery and patisserie in Seville offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI54" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Panadería y pastelería en Sevilla con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ54" s="29" t="n"/>
@@ -28603,12 +28603,12 @@
       </c>
       <c r="AH55" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Restaurant and bistro in Seville serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI55" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Restaurante y bistró en Sevilla con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ55" s="29" t="n"/>
@@ -28862,12 +28862,12 @@
       </c>
       <c r="AH56" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Pizzeria in Zaragoza serving pizza, savoury oven-baked dishes, and Italian-inspired food.</t>
         </is>
       </c>
       <c r="AI56" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Pizzería en Zaragoza con pizza, platos al horno y cocina de inspiración italiana.</t>
         </is>
       </c>
       <c r="AJ56" s="29" t="n"/>
@@ -29121,12 +29121,12 @@
       </c>
       <c r="AH57" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Restaurant and bistro in Zaragoza serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI57" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Restaurante y bistró en Zaragoza con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ57" s="29" t="n"/>
@@ -29372,12 +29372,12 @@
       </c>
       <c r="AH58" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Restaurant and bistro in Zaragoza serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI58" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Restaurante y bistró en Zaragoza con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ58" s="29" t="n"/>
@@ -29623,12 +29623,12 @@
       </c>
       <c r="AH59" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Bakery and patisserie in Málaga offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI59" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Panadería y pastelería en Málaga con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ59" s="29" t="n"/>
@@ -29870,12 +29870,12 @@
       </c>
       <c r="AH60" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Restaurant and bistro in Málaga serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI60" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Restaurante y bistró en Málaga con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ60" s="29" t="n"/>
@@ -30125,12 +30125,12 @@
       </c>
       <c r="AH61" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Bakery and patisserie in Murcia offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI61" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Panadería y pastelería en Murcia con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ61" s="29" t="n"/>
@@ -30376,12 +30376,12 @@
       </c>
       <c r="AH62" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Bakery and patisserie in Murcia offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI62" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Panadería y pastelería en Murcia con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ62" s="29" t="n"/>
@@ -30631,12 +30631,12 @@
       </c>
       <c r="AH63" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Bakery and patisserie in Lorca offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI63" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Panadería y pastelería en Lorca con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ63" s="29" t="n"/>
@@ -30890,12 +30890,12 @@
       </c>
       <c r="AH64" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Bakery and patisserie in Cartagena offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI64" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Panadería y pastelería en Cartagena con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ64" s="29" t="n"/>
@@ -31145,12 +31145,12 @@
       </c>
       <c r="AH65" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Restaurant and bistro in Las Palmas de Gran Canaria serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI65" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Restaurante y bistró en Las Palmas de Gran Canaria con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ65" s="29" t="n"/>
@@ -31400,12 +31400,12 @@
       </c>
       <c r="AH66" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Restaurant and bistro in Bilbao serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI66" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Restaurante y bistró en Bilbao con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ66" s="29" t="n"/>
@@ -31655,12 +31655,12 @@
       </c>
       <c r="AH67" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Health-focused restaurant and café in Bilbao offering bowls, brunch dishes, salads, savoury plates, cakes, and drinks.</t>
         </is>
       </c>
       <c r="AI67" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Restaurante y cafetería saludable en Bilbao con bowls, platos de brunch, ensaladas, platos salados, tartas y bebidas.</t>
         </is>
       </c>
       <c r="AJ67" s="29" t="n"/>
@@ -31914,12 +31914,12 @@
       </c>
       <c r="AH68" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Bakery and patisserie in Bilbao offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI68" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Panadería y pastelería en Bilbao con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ68" s="29" t="n"/>
@@ -32173,12 +32173,12 @@
       </c>
       <c r="AH69" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Restaurant and bistro in Alicante serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI69" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Restaurante y bistró en Alicante con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ69" s="29" t="n"/>
@@ -32428,12 +32428,12 @@
       </c>
       <c r="AH70" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Bakery and patisserie in Alicante offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI70" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Panadería y pastelería en Alicante con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ70" s="29" t="n"/>
@@ -32675,12 +32675,12 @@
       </c>
       <c r="AH71" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Bakery and patisserie in Alicante offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI71" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Panadería y pastelería en Alicante con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ71" s="29" t="n"/>
@@ -32922,12 +32922,12 @@
       </c>
       <c r="AH72" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Bakery and patisserie in Córdoba offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI72" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Panadería y pastelería en Córdoba con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ72" s="29" t="n"/>
@@ -33169,12 +33169,12 @@
       </c>
       <c r="AH73" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Bakery and patisserie in Córdoba offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI73" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Panadería y pastelería en Córdoba con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ73" s="29" t="n"/>
@@ -33416,12 +33416,12 @@
       </c>
       <c r="AH74" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Restaurant and bistro in Córdoba serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI74" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Restaurante y bistró en Córdoba con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ74" s="29" t="n"/>
@@ -33675,12 +33675,12 @@
       </c>
       <c r="AH75" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Restaurant and bistro in Valladolid serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
         </is>
       </c>
       <c r="AI75" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Restaurante y bistró en Valladolid con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
         </is>
       </c>
       <c r="AJ75" s="29" t="n"/>
@@ -33930,12 +33930,12 @@
       </c>
       <c r="AH76" s="29" t="inlineStr">
         <is>
-          <t>Verified 100% gluten-free venue based on official, association or specialist evidence.</t>
+          <t>Bakery and patisserie in Valladolid offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
         </is>
       </c>
       <c r="AI76" s="29" t="inlineStr">
         <is>
-          <t>Local verificado como 100% sin gluten según fuente oficial, asociación o directorio especializado.</t>
+          <t>Panadería y pastelería en Valladolid con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
         </is>
       </c>
       <c r="AJ76" s="29" t="n"/>
@@ -34191,8 +34191,16 @@
           <t>Japanisches Restaurant in Madrid mit Sushi, warmen japanischen Gerichten, Reisgerichten und Desserts.</t>
         </is>
       </c>
-      <c r="AH77" s="29" t="n"/>
-      <c r="AI77" s="29" t="n"/>
+      <c r="AH77" s="29" t="inlineStr">
+        <is>
+          <t>Japanese restaurant in Madrid serving sushi, hot Japanese dishes, rice dishes, and desserts.</t>
+        </is>
+      </c>
+      <c r="AI77" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante japonés en Madrid con sushi, platos japoneses calientes, platos de arroz y postres.</t>
+        </is>
+      </c>
       <c r="AJ77" s="29" t="n"/>
       <c r="AK77" s="29" t="b">
         <v>1</v>
@@ -34446,8 +34454,16 @@
           <t>Japanisches Restaurant in Madrid mit Sushi, warmen japanischen Gerichten, Reisgerichten und Desserts.</t>
         </is>
       </c>
-      <c r="AH78" s="29" t="n"/>
-      <c r="AI78" s="29" t="n"/>
+      <c r="AH78" s="29" t="inlineStr">
+        <is>
+          <t>Japanese restaurant in Madrid serving sushi, hot Japanese dishes, rice dishes, and desserts.</t>
+        </is>
+      </c>
+      <c r="AI78" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante japonés en Madrid con sushi, platos japoneses calientes, platos de arroz y postres.</t>
+        </is>
+      </c>
       <c r="AJ78" s="29" t="n"/>
       <c r="AK78" s="29" t="b">
         <v>1</v>
@@ -34705,8 +34721,16 @@
           <t>Restaurant/Bistro in Alcobendas mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
-      <c r="AH79" s="29" t="n"/>
-      <c r="AI79" s="29" t="n"/>
+      <c r="AH79" s="29" t="inlineStr">
+        <is>
+          <t>Restaurant and bistro in Alcobendas serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
+        </is>
+      </c>
+      <c r="AI79" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante y bistró en Alcobendas con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
+        </is>
+      </c>
       <c r="AJ79" s="29" t="n"/>
       <c r="AK79" s="29" t="b">
         <v>1</v>
@@ -34948,8 +34972,16 @@
           <t>Restaurant in Granada mit regionaler Küche, Hauptgerichten, Vorspeisen, Desserts und saisonalen Speisen.</t>
         </is>
       </c>
-      <c r="AH80" s="29" t="n"/>
-      <c r="AI80" s="29" t="n"/>
+      <c r="AH80" s="29" t="inlineStr">
+        <is>
+          <t>Restaurant in Granada serving regional cuisine, main courses, starters, desserts, and seasonal dishes.</t>
+        </is>
+      </c>
+      <c r="AI80" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante en Granada con cocina regional, platos principales, entrantes, postres y platos de temporada.</t>
+        </is>
+      </c>
       <c r="AJ80" s="29" t="n"/>
       <c r="AK80" s="29" t="b">
         <v>1</v>
@@ -35191,8 +35223,16 @@
           <t>Italienisches Restaurant in Granada mit Pizza, Pasta, Antipasti und weiteren mediterranen Gerichten.</t>
         </is>
       </c>
-      <c r="AH81" s="29" t="n"/>
-      <c r="AI81" s="29" t="n"/>
+      <c r="AH81" s="29" t="inlineStr">
+        <is>
+          <t>Italian restaurant in Granada serving pizza, pasta, antipasti, and other Mediterranean dishes.</t>
+        </is>
+      </c>
+      <c r="AI81" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante italiano en Granada con pizza, pasta, antipasti y otros platos mediterráneos.</t>
+        </is>
+      </c>
       <c r="AJ81" s="29" t="n"/>
       <c r="AK81" s="29" t="b">
         <v>1</v>
@@ -35442,8 +35482,16 @@
           <t>Restaurant in Oviedo mit Tapas, mediterranen Gerichten, Fisch-/Fleischspeisen und spanisch inspirierten Klassikern.</t>
         </is>
       </c>
-      <c r="AH82" s="29" t="n"/>
-      <c r="AI82" s="29" t="n"/>
+      <c r="AH82" s="29" t="inlineStr">
+        <is>
+          <t>Restaurant in Oviedo serving tapas, Mediterranean dishes, fish and meat specialities, and Spanish-inspired classics.</t>
+        </is>
+      </c>
+      <c r="AI82" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante en Oviedo con tapas, platos mediterráneos, pescados y carnes, y clásicos de inspiración española.</t>
+        </is>
+      </c>
       <c r="AJ82" s="29" t="n"/>
       <c r="AK82" s="29" t="b">
         <v>1</v>
@@ -35693,8 +35741,16 @@
           <t>Restaurant in Gijón mit regionaler Küche, Hauptgerichten, Vorspeisen, Desserts und saisonalen Speisen.</t>
         </is>
       </c>
-      <c r="AH83" s="29" t="n"/>
-      <c r="AI83" s="29" t="n"/>
+      <c r="AH83" s="29" t="inlineStr">
+        <is>
+          <t>Restaurant in Gijón serving regional cuisine, main courses, starters, desserts, and seasonal dishes.</t>
+        </is>
+      </c>
+      <c r="AI83" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante en Gijón con cocina regional, platos principales, entrantes, postres y platos de temporada.</t>
+        </is>
+      </c>
       <c r="AJ83" s="29" t="n"/>
       <c r="AK83" s="29" t="b">
         <v>1</v>
@@ -35944,8 +36000,16 @@
           <t>Restaurant in Zamora mit regionaler Küche, Hauptgerichten, Vorspeisen, Desserts und saisonalen Speisen.</t>
         </is>
       </c>
-      <c r="AH84" s="29" t="n"/>
-      <c r="AI84" s="29" t="n"/>
+      <c r="AH84" s="29" t="inlineStr">
+        <is>
+          <t>Restaurant in Zamora serving regional cuisine, main courses, starters, desserts, and seasonal dishes.</t>
+        </is>
+      </c>
+      <c r="AI84" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante en Zamora con cocina regional, platos principales, entrantes, postres y platos de temporada.</t>
+        </is>
+      </c>
       <c r="AJ84" s="29" t="n"/>
       <c r="AK84" s="29" t="b">
         <v>1</v>
@@ -36191,8 +36255,16 @@
           <t>Restaurant/Bistro in A Coruña mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
-      <c r="AH85" s="29" t="n"/>
-      <c r="AI85" s="29" t="n"/>
+      <c r="AH85" s="29" t="inlineStr">
+        <is>
+          <t>Restaurant and bistro in A Coruña serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
+        </is>
+      </c>
+      <c r="AI85" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante y bistró en A Coruña con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
+        </is>
+      </c>
       <c r="AJ85" s="29" t="n"/>
       <c r="AK85" s="29" t="b">
         <v>1</v>
@@ -36438,8 +36510,16 @@
           <t>Bäckerei/Patisserie in Granollers mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH86" s="29" t="n"/>
-      <c r="AI86" s="29" t="n"/>
+      <c r="AH86" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Granollers offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI86" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Granollers con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ86" s="29" t="n"/>
       <c r="AK86" s="29" t="b">
         <v>1</v>
@@ -36685,8 +36765,16 @@
           <t>Bäckerei/Patisserie in Sant Cugat del Vallès mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH87" s="29" t="n"/>
-      <c r="AI87" s="29" t="n"/>
+      <c r="AH87" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Sant Cugat del Vallès offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI87" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Sant Cugat del Vallès con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ87" s="29" t="n"/>
       <c r="AK87" s="29" t="b">
         <v>1</v>
@@ -36928,8 +37016,16 @@
           <t>Bäckerei/Patisserie in Sabadell mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH88" s="29" t="n"/>
-      <c r="AI88" s="29" t="n"/>
+      <c r="AH88" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Sabadell offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI88" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Sabadell con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ88" s="29" t="n"/>
       <c r="AK88" s="29" t="b">
         <v>1</v>
@@ -37175,8 +37271,16 @@
           <t>Bäckerei/Patisserie in Olesa de Montserrat mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH89" s="29" t="n"/>
-      <c r="AI89" s="29" t="n"/>
+      <c r="AH89" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Olesa de Montserrat offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI89" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Olesa de Montserrat con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ89" s="29" t="n"/>
       <c r="AK89" s="29" t="b">
         <v>1</v>
@@ -37422,8 +37526,16 @@
           <t>Bäckerei/Patisserie in Vic mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH90" s="29" t="n"/>
-      <c r="AI90" s="29" t="n"/>
+      <c r="AH90" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Vic offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI90" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Vic con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ90" s="29" t="n"/>
       <c r="AK90" s="29" t="b">
         <v>1</v>
@@ -37669,8 +37781,16 @@
           <t>Bäckerei/Patisserie in Jerez de la Frontera mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH91" s="29" t="n"/>
-      <c r="AI91" s="29" t="n"/>
+      <c r="AH91" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Jerez de la Frontera offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI91" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Jerez de la Frontera con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ91" s="29" t="n"/>
       <c r="AK91" s="29" t="b">
         <v>1</v>
@@ -37908,8 +38028,16 @@
           <t>Bäckerei/Patisserie in Teruel mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH92" s="29" t="n"/>
-      <c r="AI92" s="29" t="n"/>
+      <c r="AH92" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Teruel offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI92" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Teruel con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ92" s="29" t="n"/>
       <c r="AK92" s="29" t="b">
         <v>1</v>
@@ -38151,8 +38279,16 @@
           <t>Restaurant/Bistro in Peñíscola mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
-      <c r="AH93" s="29" t="n"/>
-      <c r="AI93" s="29" t="n"/>
+      <c r="AH93" s="29" t="inlineStr">
+        <is>
+          <t>Restaurant and bistro in Peñíscola serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
+        </is>
+      </c>
+      <c r="AI93" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante y bistró en Peñíscola con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
+        </is>
+      </c>
       <c r="AJ93" s="29" t="n"/>
       <c r="AK93" s="29" t="b">
         <v>1</v>
@@ -38394,8 +38530,16 @@
           <t>Bäckerei/Patisserie in Toledo mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH94" s="29" t="n"/>
-      <c r="AI94" s="29" t="n"/>
+      <c r="AH94" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Toledo offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI94" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Toledo con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ94" s="29" t="n"/>
       <c r="AK94" s="29" t="b">
         <v>1</v>
@@ -38633,8 +38777,16 @@
           <t>Bäckerei/Patisserie in Pontevedra mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH95" s="29" t="n"/>
-      <c r="AI95" s="29" t="n"/>
+      <c r="AH95" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Pontevedra offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI95" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Pontevedra con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ95" s="29" t="n"/>
       <c r="AK95" s="29" t="b">
         <v>1</v>
@@ -38876,8 +39028,16 @@
           <t>Bäckerei/Patisserie in Valencia mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH96" s="29" t="n"/>
-      <c r="AI96" s="29" t="n"/>
+      <c r="AH96" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Valencia offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI96" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Valencia con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ96" s="29" t="n"/>
       <c r="AK96" s="29" t="b">
         <v>1</v>
@@ -39111,8 +39271,16 @@
           <t>Café in Fuentenava de Jábaga mit Kaffee, Frühstück, Kuchen, Gebäck, Brunchgerichten und kleinen Speisen.</t>
         </is>
       </c>
-      <c r="AH97" s="29" t="n"/>
-      <c r="AI97" s="29" t="n"/>
+      <c r="AH97" s="29" t="inlineStr">
+        <is>
+          <t>Café in Fuentenava de Jábaga offering coffee, breakfast, cakes, pastries, brunch dishes, and light bites.</t>
+        </is>
+      </c>
+      <c r="AI97" s="29" t="inlineStr">
+        <is>
+          <t>Cafetería en Fuentenava de Jábaga con café, desayunos, tartas, bollería, platos de brunch y comidas ligeras.</t>
+        </is>
+      </c>
       <c r="AJ97" s="29" t="n"/>
       <c r="AK97" s="29" t="b">
         <v>1</v>
@@ -39358,8 +39526,16 @@
           <t>Bäckerei/Patisserie in Vigo mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH98" s="29" t="n"/>
-      <c r="AI98" s="29" t="n"/>
+      <c r="AH98" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Vigo offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI98" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Vigo con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ98" s="29" t="n"/>
       <c r="AK98" s="29" t="b">
         <v>1</v>
@@ -39601,8 +39777,16 @@
           <t>Bäckerei/Patisserie in Barcelona mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH99" s="29" t="n"/>
-      <c r="AI99" s="29" t="n"/>
+      <c r="AH99" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Barcelona offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI99" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Barcelona con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ99" s="29" t="n"/>
       <c r="AK99" s="29" t="b">
         <v>1</v>
@@ -39852,8 +40036,16 @@
           <t>Bäckerei/Patisserie in Barcelona mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH100" s="29" t="n"/>
-      <c r="AI100" s="29" t="n"/>
+      <c r="AH100" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Barcelona offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI100" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Barcelona con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ100" s="29" t="n"/>
       <c r="AK100" s="29" t="b">
         <v>1</v>
@@ -40103,8 +40295,16 @@
           <t>Bäckerei/Patisserie in Barcelona mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH101" s="29" t="n"/>
-      <c r="AI101" s="29" t="n"/>
+      <c r="AH101" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Barcelona offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI101" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Barcelona con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ101" s="29" t="n"/>
       <c r="AK101" s="29" t="b">
         <v>1</v>
@@ -40346,8 +40546,16 @@
           <t>Veganes bzw. plant-based Café/Restaurant in Barcelona mit Bowls, Kuchen, Frühstücksgerichten, Snacks und kreativer pflanzlicher Küche.</t>
         </is>
       </c>
-      <c r="AH102" s="29" t="n"/>
-      <c r="AI102" s="29" t="n"/>
+      <c r="AH102" s="29" t="inlineStr">
+        <is>
+          <t>Vegan, plant-based café and restaurant in Barcelona offering bowls, cakes, breakfast dishes, snacks, and creative plant-based cuisine.</t>
+        </is>
+      </c>
+      <c r="AI102" s="29" t="inlineStr">
+        <is>
+          <t>Cafetería y restaurante vegano en Barcelona con bowls, tartas, desayunos, snacks y cocina vegetal creativa.</t>
+        </is>
+      </c>
       <c r="AJ102" s="29" t="n"/>
       <c r="AK102" s="29" t="b">
         <v>1</v>
@@ -40589,8 +40797,16 @@
           <t>Bäckerei/Patisserie in Palma mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH103" s="29" t="n"/>
-      <c r="AI103" s="29" t="n"/>
+      <c r="AH103" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Palma offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI103" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Palma con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ103" s="29" t="n"/>
       <c r="AK103" s="29" t="b">
         <v>1</v>
@@ -40840,8 +41056,16 @@
           <t>Veganes bzw. plant-based Café/Restaurant in Santa Ponça mit Bowls, Kuchen, Frühstücksgerichten, Snacks und kreativer pflanzlicher Küche.</t>
         </is>
       </c>
-      <c r="AH104" s="29" t="n"/>
-      <c r="AI104" s="29" t="n"/>
+      <c r="AH104" s="29" t="inlineStr">
+        <is>
+          <t>Vegan, plant-based café and restaurant in Santa Ponça offering bowls, cakes, breakfast dishes, snacks, and creative plant-based cuisine.</t>
+        </is>
+      </c>
+      <c r="AI104" s="29" t="inlineStr">
+        <is>
+          <t>Cafetería y restaurante vegano en Santa Ponça con bowls, tartas, desayunos, snacks y cocina vegetal creativa.</t>
+        </is>
+      </c>
       <c r="AJ104" s="29" t="n"/>
       <c r="AK104" s="29" t="b">
         <v>1</v>
@@ -41079,8 +41303,16 @@
           <t>Café in Palma mit Kaffee, Frühstück, Kuchen, Gebäck, Brunchgerichten und kleinen Speisen.</t>
         </is>
       </c>
-      <c r="AH105" s="29" t="n"/>
-      <c r="AI105" s="29" t="n"/>
+      <c r="AH105" s="29" t="inlineStr">
+        <is>
+          <t>Café in Palma offering coffee, breakfast, cakes, pastries, brunch dishes, and light bites.</t>
+        </is>
+      </c>
+      <c r="AI105" s="29" t="inlineStr">
+        <is>
+          <t>Cafetería en Palma con café, desayunos, tartas, bollería, platos de brunch y comidas ligeras.</t>
+        </is>
+      </c>
       <c r="AJ105" s="29" t="n"/>
       <c r="AK105" s="29" t="b">
         <v>1</v>
@@ -41318,8 +41550,16 @@
           <t>Bäckerei/Patisserie in Alicante mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH106" s="29" t="n"/>
-      <c r="AI106" s="29" t="n"/>
+      <c r="AH106" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Alicante offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI106" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Alicante con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ106" s="29" t="n"/>
       <c r="AK106" s="29" t="b">
         <v>1</v>
@@ -41561,8 +41801,16 @@
           <t>Bäckerei/Patisserie in Pineda de Mar mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH107" s="29" t="n"/>
-      <c r="AI107" s="29" t="n"/>
+      <c r="AH107" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Pineda de Mar offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI107" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Pineda de Mar con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ107" s="29" t="n"/>
       <c r="AK107" s="29" t="b">
         <v>1</v>
@@ -41804,8 +42052,16 @@
           <t>Bäckerei/Patisserie in A Coruña mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH108" s="29" t="n"/>
-      <c r="AI108" s="29" t="n"/>
+      <c r="AH108" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in A Coruña offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI108" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en A Coruña con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ108" s="29" t="n"/>
       <c r="AK108" s="29" t="b">
         <v>1</v>
@@ -42043,8 +42299,16 @@
           <t>Bäckerei/Patisserie in A Coruña mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH109" s="29" t="n"/>
-      <c r="AI109" s="29" t="n"/>
+      <c r="AH109" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in A Coruña offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI109" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en A Coruña con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ109" s="29" t="n"/>
       <c r="AK109" s="29" t="b">
         <v>1</v>
@@ -42282,8 +42546,16 @@
           <t>Bäckerei/Patisserie in A Coruña mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH110" s="29" t="n"/>
-      <c r="AI110" s="29" t="n"/>
+      <c r="AH110" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in A Coruña offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI110" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en A Coruña con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ110" s="29" t="n"/>
       <c r="AK110" s="29" t="b">
         <v>1</v>
@@ -42521,8 +42793,16 @@
           <t>Bäckerei/Patisserie in A Coruña mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH111" s="29" t="n"/>
-      <c r="AI111" s="29" t="n"/>
+      <c r="AH111" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in A Coruña offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI111" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en A Coruña con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ111" s="29" t="n"/>
       <c r="AK111" s="29" t="b">
         <v>1</v>
@@ -42760,8 +43040,16 @@
           <t>Café in A Coruña mit Kaffee, Frühstück, Kuchen, Gebäck, Brunchgerichten und kleinen Speisen.</t>
         </is>
       </c>
-      <c r="AH112" s="29" t="n"/>
-      <c r="AI112" s="29" t="n"/>
+      <c r="AH112" s="29" t="inlineStr">
+        <is>
+          <t>Café in A Coruña offering coffee, breakfast, cakes, pastries, brunch dishes, and light bites.</t>
+        </is>
+      </c>
+      <c r="AI112" s="29" t="inlineStr">
+        <is>
+          <t>Cafetería en A Coruña con café, desayunos, tartas, bollería, platos de brunch y comidas ligeras.</t>
+        </is>
+      </c>
       <c r="AJ112" s="29" t="n"/>
       <c r="AK112" s="29" t="b">
         <v>1</v>
@@ -42999,8 +43287,16 @@
           <t>Mexikanisches Restaurant in A Coruña mit Tacos, Nachos, Salsas, Bowls und weiteren mexikanischen Klassikern.</t>
         </is>
       </c>
-      <c r="AH113" s="29" t="n"/>
-      <c r="AI113" s="29" t="n"/>
+      <c r="AH113" s="29" t="inlineStr">
+        <is>
+          <t>Mexican restaurant in A Coruña serving tacos, nachos, salsas, bowls, and other Mexican classics.</t>
+        </is>
+      </c>
+      <c r="AI113" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante mexicano en A Coruña con tacos, nachos, salsas, bowls y otros clásicos mexicanos.</t>
+        </is>
+      </c>
       <c r="AJ113" s="29" t="n"/>
       <c r="AK113" s="29" t="b">
         <v>1</v>
@@ -43238,8 +43534,16 @@
           <t>Italienisches Restaurant in A Coruña mit Pizza, Pasta, Antipasti und weiteren mediterranen Gerichten.</t>
         </is>
       </c>
-      <c r="AH114" s="29" t="n"/>
-      <c r="AI114" s="29" t="n"/>
+      <c r="AH114" s="29" t="inlineStr">
+        <is>
+          <t>Italian restaurant in A Coruña serving pizza, pasta, antipasti, and other Mediterranean dishes.</t>
+        </is>
+      </c>
+      <c r="AI114" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante italiano en A Coruña con pizza, pasta, antipasti y otros platos mediterráneos.</t>
+        </is>
+      </c>
       <c r="AJ114" s="29" t="n"/>
       <c r="AK114" s="29" t="b">
         <v>1</v>
@@ -43477,8 +43781,16 @@
           <t>Restaurant in Asiego mit regionaler Küche, Hauptgerichten, Vorspeisen, Desserts und saisonalen Speisen.</t>
         </is>
       </c>
-      <c r="AH115" s="29" t="n"/>
-      <c r="AI115" s="29" t="n"/>
+      <c r="AH115" s="29" t="inlineStr">
+        <is>
+          <t>Restaurant in Asiego serving regional cuisine, main courses, starters, desserts, and seasonal dishes.</t>
+        </is>
+      </c>
+      <c r="AI115" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante en Asiego con cocina regional, platos principales, entrantes, postres y platos de temporada.</t>
+        </is>
+      </c>
       <c r="AJ115" s="29" t="n"/>
       <c r="AK115" s="29" t="b">
         <v>1</v>
@@ -43720,8 +44032,16 @@
           <t>Restaurant in Santa Cruz de Tenerife mit regionaler Küche, Hauptgerichten, Vorspeisen, Desserts und saisonalen Speisen.</t>
         </is>
       </c>
-      <c r="AH116" s="29" t="n"/>
-      <c r="AI116" s="29" t="n"/>
+      <c r="AH116" s="29" t="inlineStr">
+        <is>
+          <t>Restaurant in Santa Cruz de Tenerife serving regional cuisine, main courses, starters, desserts, and seasonal dishes.</t>
+        </is>
+      </c>
+      <c r="AI116" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante en Santa Cruz de Tenerife con cocina regional, platos principales, entrantes, postres y platos de temporada.</t>
+        </is>
+      </c>
       <c r="AJ116" s="29" t="n"/>
       <c r="AK116" s="29" t="b">
         <v>1</v>
@@ -43963,8 +44283,16 @@
           <t>Restaurant/Bistro in Los Cristianos mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
-      <c r="AH117" s="29" t="n"/>
-      <c r="AI117" s="29" t="n"/>
+      <c r="AH117" s="29" t="inlineStr">
+        <is>
+          <t>Restaurant and bistro in Los Cristianos serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
+        </is>
+      </c>
+      <c r="AI117" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante y bistró en Los Cristianos con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
+        </is>
+      </c>
       <c r="AJ117" s="29" t="n"/>
       <c r="AK117" s="29" t="b">
         <v>1</v>
@@ -44206,8 +44534,16 @@
           <t>Restaurant/Bistro in La Orotava mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
-      <c r="AH118" s="29" t="n"/>
-      <c r="AI118" s="29" t="n"/>
+      <c r="AH118" s="29" t="inlineStr">
+        <is>
+          <t>Restaurant and bistro in La Orotava serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
+        </is>
+      </c>
+      <c r="AI118" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante y bistró en La Orotava con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
+        </is>
+      </c>
       <c r="AJ118" s="29" t="n"/>
       <c r="AK118" s="29" t="b">
         <v>1</v>
@@ -44453,8 +44789,16 @@
           <t>Restaurant/Bistro in San Cristóbal de La Laguna mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
-      <c r="AH119" s="29" t="n"/>
-      <c r="AI119" s="29" t="n"/>
+      <c r="AH119" s="29" t="inlineStr">
+        <is>
+          <t>Restaurant and bistro in San Cristóbal de La Laguna serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
+        </is>
+      </c>
+      <c r="AI119" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante y bistró en San Cristóbal de La Laguna con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
+        </is>
+      </c>
       <c r="AJ119" s="29" t="n"/>
       <c r="AK119" s="29" t="b">
         <v>1</v>
@@ -44696,8 +45040,16 @@
           <t>Restaurant in San Cristóbal de La Laguna mit regionaler Küche, Hauptgerichten, Vorspeisen, Desserts und saisonalen Speisen.</t>
         </is>
       </c>
-      <c r="AH120" s="29" t="n"/>
-      <c r="AI120" s="29" t="n"/>
+      <c r="AH120" s="29" t="inlineStr">
+        <is>
+          <t>Restaurant in San Cristóbal de La Laguna serving regional cuisine, main courses, starters, desserts, and seasonal dishes.</t>
+        </is>
+      </c>
+      <c r="AI120" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante en San Cristóbal de La Laguna con cocina regional, platos principales, entrantes, postres y platos de temporada.</t>
+        </is>
+      </c>
       <c r="AJ120" s="29" t="n"/>
       <c r="AK120" s="29" t="b">
         <v>1</v>
@@ -44935,8 +45287,16 @@
           <t>Bäckerei/Patisserie in San Cristóbal de La Laguna mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH121" s="29" t="n"/>
-      <c r="AI121" s="29" t="n"/>
+      <c r="AH121" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in San Cristóbal de La Laguna offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI121" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en San Cristóbal de La Laguna con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ121" s="29" t="n"/>
       <c r="AK121" s="29" t="b">
         <v>1</v>
@@ -45174,8 +45534,16 @@
           <t>Bäckerei/Patisserie in Ourense mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH122" s="29" t="n"/>
-      <c r="AI122" s="29" t="n"/>
+      <c r="AH122" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Ourense offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI122" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Ourense con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ122" s="29" t="n"/>
       <c r="AK122" s="29" t="b">
         <v>1</v>
@@ -45417,8 +45785,16 @@
           <t>Bäckerei/Patisserie in Castuera mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH123" s="29" t="n"/>
-      <c r="AI123" s="29" t="n"/>
+      <c r="AH123" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Castuera offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI123" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Castuera con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ123" s="29" t="n"/>
       <c r="AK123" s="29" t="b">
         <v>1</v>
@@ -45656,8 +46032,16 @@
           <t>Bäckerei/Patisserie in Madrid mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH124" s="29" t="n"/>
-      <c r="AI124" s="29" t="n"/>
+      <c r="AH124" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Madrid offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI124" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Madrid con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ124" s="29" t="n"/>
       <c r="AK124" s="29" t="b">
         <v>1</v>
@@ -45895,8 +46279,16 @@
           <t>Bäckerei/Patisserie in Boadilla del Monte mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH125" s="29" t="n"/>
-      <c r="AI125" s="29" t="n"/>
+      <c r="AH125" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Boadilla del Monte offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI125" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Boadilla del Monte con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ125" s="29" t="n"/>
       <c r="AK125" s="29" t="b">
         <v>1</v>
@@ -46138,8 +46530,16 @@
           <t>Bäckerei/Patisserie in Vilanova i la Geltrú mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH126" s="29" t="n"/>
-      <c r="AI126" s="29" t="n"/>
+      <c r="AH126" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Vilanova i la Geltrú offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI126" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Vilanova i la Geltrú con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ126" s="29" t="n"/>
       <c r="AK126" s="29" t="b">
         <v>1</v>
@@ -46381,8 +46781,16 @@
           <t>Bäckerei/Patisserie in Madridejos mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH127" s="29" t="n"/>
-      <c r="AI127" s="29" t="n"/>
+      <c r="AH127" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Madridejos offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI127" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Madridejos con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ127" s="29" t="n"/>
       <c r="AK127" s="29" t="b">
         <v>1</v>
@@ -46616,8 +47024,16 @@
           <t>Bäckerei/Patisserie in Madrid mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH128" s="29" t="n"/>
-      <c r="AI128" s="29" t="n"/>
+      <c r="AH128" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Madrid offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI128" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Madrid con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ128" s="29" t="n"/>
       <c r="AK128" s="29" t="b">
         <v>1</v>
@@ -46859,8 +47275,16 @@
           <t>Bäckerei/Patisserie in Cabrera de Mar mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
         </is>
       </c>
-      <c r="AH129" s="29" t="n"/>
-      <c r="AI129" s="29" t="n"/>
+      <c r="AH129" s="29" t="inlineStr">
+        <is>
+          <t>Bakery and patisserie in Cabrera de Mar offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+        </is>
+      </c>
+      <c r="AI129" s="29" t="inlineStr">
+        <is>
+          <t>Panadería y pastelería en Cabrera de Mar con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+        </is>
+      </c>
       <c r="AJ129" s="29" t="n"/>
       <c r="AK129" s="29" t="b">
         <v>1</v>
@@ -47090,8 +47514,16 @@
           <t>Restaurant/Bistro in Isla Cristina mit Vorspeisen, Hauptgerichten, Desserts und je nach Konzept regionaler, mediterraner oder internationaler Küche.</t>
         </is>
       </c>
-      <c r="AH130" s="29" t="n"/>
-      <c r="AI130" s="29" t="n"/>
+      <c r="AH130" s="29" t="inlineStr">
+        <is>
+          <t>Restaurant and bistro in Isla Cristina serving starters, main courses, and desserts, with regional, Mediterranean, or international cuisine depending on the concept.</t>
+        </is>
+      </c>
+      <c r="AI130" s="29" t="inlineStr">
+        <is>
+          <t>Restaurante y bistró en Isla Cristina con entrantes, platos principales y postres; cocina regional, mediterránea o internacional según el concepto.</t>
+        </is>
+      </c>
       <c r="AJ130" s="29" t="n"/>
       <c r="AK130" s="29" t="b">
         <v>1</v>

--- a/data-source/CeliacSafe_Datenbank_v4_Spain_129_geocoded.xlsx
+++ b/data-source/CeliacSafe_Datenbank_v4_Spain_129_geocoded.xlsx
@@ -36507,17 +36507,17 @@
       <c r="AF86" s="29" t="n"/>
       <c r="AG86" s="29" t="inlineStr">
         <is>
-          <t>Bäckerei/Patisserie in Granollers mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
+          <t>100% glutenfreies KrümCoffee-Café in Granollers mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH86" s="29" t="inlineStr">
         <is>
-          <t>Bakery and patisserie in Granollers offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+          <t>100% gluten-free KrümCoffee café in Granollers serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
         </is>
       </c>
       <c r="AI86" s="29" t="inlineStr">
         <is>
-          <t>Panadería y pastelería en Granollers con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+          <t>Cafetería KrümCoffee 100% sin gluten en Granollers con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
         </is>
       </c>
       <c r="AJ86" s="29" t="n"/>
@@ -36762,17 +36762,17 @@
       <c r="AF87" s="29" t="n"/>
       <c r="AG87" s="29" t="inlineStr">
         <is>
-          <t>Bäckerei/Patisserie in Sant Cugat del Vallès mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
+          <t>100% glutenfreies KrümCoffee-Café in Sant Cugat del Vallès mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH87" s="29" t="inlineStr">
         <is>
-          <t>Bakery and patisserie in Sant Cugat del Vallès offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+          <t>100% gluten-free KrümCoffee café in Sant Cugat del Vallès serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
         </is>
       </c>
       <c r="AI87" s="29" t="inlineStr">
         <is>
-          <t>Panadería y pastelería en Sant Cugat del Vallès con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+          <t>Cafetería KrümCoffee 100% sin gluten en Sant Cugat del Vallès con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
         </is>
       </c>
       <c r="AJ87" s="29" t="n"/>
@@ -37013,17 +37013,17 @@
       <c r="AF88" s="29" t="n"/>
       <c r="AG88" s="29" t="inlineStr">
         <is>
-          <t>Bäckerei/Patisserie in Sabadell mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
+          <t>100% glutenfreies KrümCoffee-Café in Sabadell mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH88" s="29" t="inlineStr">
         <is>
-          <t>Bakery and patisserie in Sabadell offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+          <t>100% gluten-free KrümCoffee café in Sabadell serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
         </is>
       </c>
       <c r="AI88" s="29" t="inlineStr">
         <is>
-          <t>Panadería y pastelería en Sabadell con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+          <t>Cafetería KrümCoffee 100% sin gluten en Sabadell con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
         </is>
       </c>
       <c r="AJ88" s="29" t="n"/>
@@ -37268,17 +37268,17 @@
       <c r="AF89" s="29" t="n"/>
       <c r="AG89" s="29" t="inlineStr">
         <is>
-          <t>Bäckerei/Patisserie in Olesa de Montserrat mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
+          <t>100% glutenfreies KrümCoffee-Café in Olesa de Montserrat mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH89" s="29" t="inlineStr">
         <is>
-          <t>Bakery and patisserie in Olesa de Montserrat offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+          <t>100% gluten-free KrümCoffee café in Olesa de Montserrat serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
         </is>
       </c>
       <c r="AI89" s="29" t="inlineStr">
         <is>
-          <t>Panadería y pastelería en Olesa de Montserrat con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+          <t>Cafetería KrümCoffee 100% sin gluten en Olesa de Montserrat con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
         </is>
       </c>
       <c r="AJ89" s="29" t="n"/>
@@ -37523,17 +37523,17 @@
       <c r="AF90" s="29" t="n"/>
       <c r="AG90" s="29" t="inlineStr">
         <is>
-          <t>Bäckerei/Patisserie in Vic mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
+          <t>100% glutenfreies KrümCoffee-Café in Vic mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH90" s="29" t="inlineStr">
         <is>
-          <t>Bakery and patisserie in Vic offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+          <t>100% gluten-free KrümCoffee café in Vic serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
         </is>
       </c>
       <c r="AI90" s="29" t="inlineStr">
         <is>
-          <t>Panadería y pastelería en Vic con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+          <t>Cafetería KrümCoffee 100% sin gluten en Vic con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
         </is>
       </c>
       <c r="AJ90" s="29" t="n"/>
@@ -37778,17 +37778,17 @@
       <c r="AF91" s="29" t="n"/>
       <c r="AG91" s="29" t="inlineStr">
         <is>
-          <t>Bäckerei/Patisserie in Jerez de la Frontera mit Brot, Brötchen, Kuchen, Torten, Gebäck, süßen Backwaren und teilweise herzhaften Snacks.</t>
+          <t>100% glutenfreies KrümCoffee-Café in Jerez de la Frontera mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH91" s="29" t="inlineStr">
         <is>
-          <t>Bakery and patisserie in Jerez de la Frontera offering bread, rolls, cakes, tarts, pastries, sweet baked goods, and a selection of savoury snacks.</t>
+          <t>100% gluten-free KrümCoffee café in Jerez de la Frontera serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
         </is>
       </c>
       <c r="AI91" s="29" t="inlineStr">
         <is>
-          <t>Panadería y pastelería en Jerez de la Frontera con pan, panecillos, tartas, pasteles, bollería, dulces y algunos snacks salados.</t>
+          <t>Cafetería KrümCoffee 100% sin gluten en Jerez de la Frontera con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
         </is>
       </c>
       <c r="AJ91" s="29" t="n"/>

--- a/data-source/CeliacSafe_Datenbank_v4_Spain_129_geocoded.xlsx
+++ b/data-source/CeliacSafe_Datenbank_v4_Spain_129_geocoded.xlsx
@@ -36507,17 +36507,17 @@
       <c r="AF86" s="29" t="n"/>
       <c r="AG86" s="29" t="inlineStr">
         <is>
-          <t>100% glutenfreies KrümCoffee-Café in Granollers mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
+          <t>KrümCoffee-Café in Granollers mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH86" s="29" t="inlineStr">
         <is>
-          <t>100% gluten-free KrümCoffee café in Granollers serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
+          <t>KrümCoffee café in Granollers serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
         </is>
       </c>
       <c r="AI86" s="29" t="inlineStr">
         <is>
-          <t>Cafetería KrümCoffee 100% sin gluten en Granollers con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
+          <t>Cafetería KrümCoffee en Granollers con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
         </is>
       </c>
       <c r="AJ86" s="29" t="n"/>
@@ -36762,17 +36762,17 @@
       <c r="AF87" s="29" t="n"/>
       <c r="AG87" s="29" t="inlineStr">
         <is>
-          <t>100% glutenfreies KrümCoffee-Café in Sant Cugat del Vallès mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
+          <t>KrümCoffee-Café in Sant Cugat del Vallès mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH87" s="29" t="inlineStr">
         <is>
-          <t>100% gluten-free KrümCoffee café in Sant Cugat del Vallès serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
+          <t>KrümCoffee café in Sant Cugat del Vallès serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
         </is>
       </c>
       <c r="AI87" s="29" t="inlineStr">
         <is>
-          <t>Cafetería KrümCoffee 100% sin gluten en Sant Cugat del Vallès con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
+          <t>Cafetería KrümCoffee en Sant Cugat del Vallès con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
         </is>
       </c>
       <c r="AJ87" s="29" t="n"/>
@@ -37013,17 +37013,17 @@
       <c r="AF88" s="29" t="n"/>
       <c r="AG88" s="29" t="inlineStr">
         <is>
-          <t>100% glutenfreies KrümCoffee-Café in Sabadell mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
+          <t>KrümCoffee-Café in Sabadell mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH88" s="29" t="inlineStr">
         <is>
-          <t>100% gluten-free KrümCoffee café in Sabadell serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
+          <t>KrümCoffee café in Sabadell serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
         </is>
       </c>
       <c r="AI88" s="29" t="inlineStr">
         <is>
-          <t>Cafetería KrümCoffee 100% sin gluten en Sabadell con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
+          <t>Cafetería KrümCoffee en Sabadell con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
         </is>
       </c>
       <c r="AJ88" s="29" t="n"/>
@@ -37268,17 +37268,17 @@
       <c r="AF89" s="29" t="n"/>
       <c r="AG89" s="29" t="inlineStr">
         <is>
-          <t>100% glutenfreies KrümCoffee-Café in Olesa de Montserrat mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
+          <t>KrümCoffee-Café in Olesa de Montserrat mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH89" s="29" t="inlineStr">
         <is>
-          <t>100% gluten-free KrümCoffee café in Olesa de Montserrat serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
+          <t>KrümCoffee café in Olesa de Montserrat serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
         </is>
       </c>
       <c r="AI89" s="29" t="inlineStr">
         <is>
-          <t>Cafetería KrümCoffee 100% sin gluten en Olesa de Montserrat con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
+          <t>Cafetería KrümCoffee en Olesa de Montserrat con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
         </is>
       </c>
       <c r="AJ89" s="29" t="n"/>
@@ -37523,17 +37523,17 @@
       <c r="AF90" s="29" t="n"/>
       <c r="AG90" s="29" t="inlineStr">
         <is>
-          <t>100% glutenfreies KrümCoffee-Café in Vic mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
+          <t>KrümCoffee-Café in Vic mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH90" s="29" t="inlineStr">
         <is>
-          <t>100% gluten-free KrümCoffee café in Vic serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
+          <t>KrümCoffee café in Vic serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
         </is>
       </c>
       <c r="AI90" s="29" t="inlineStr">
         <is>
-          <t>Cafetería KrümCoffee 100% sin gluten en Vic con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
+          <t>Cafetería KrümCoffee en Vic con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
         </is>
       </c>
       <c r="AJ90" s="29" t="n"/>
@@ -37778,17 +37778,17 @@
       <c r="AF91" s="29" t="n"/>
       <c r="AG91" s="29" t="inlineStr">
         <is>
-          <t>100% glutenfreies KrümCoffee-Café in Jerez de la Frontera mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
+          <t>KrümCoffee-Café in Jerez de la Frontera mit Kaffee, Frühstück, Brunch, Kuchen, Gebäck und herzhaften Snacks.</t>
         </is>
       </c>
       <c r="AH91" s="29" t="inlineStr">
         <is>
-          <t>100% gluten-free KrümCoffee café in Jerez de la Frontera serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
+          <t>KrümCoffee café in Jerez de la Frontera serving coffee, breakfast, brunch, cakes, pastries, and savoury snacks.</t>
         </is>
       </c>
       <c r="AI91" s="29" t="inlineStr">
         <is>
-          <t>Cafetería KrümCoffee 100% sin gluten en Jerez de la Frontera con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
+          <t>Cafetería KrümCoffee en Jerez de la Frontera con café, desayuno, brunch, tartas, bollería y snacks salados.</t>
         </is>
       </c>
       <c r="AJ91" s="29" t="n"/>
